--- a/output/ncs.xlsx
+++ b/output/ncs.xlsx
@@ -425,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -443,9 +443,9 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,6 +540,4430 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Senior Citizen Tour pan India</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2930777</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>English Senior Citizen Tour Assistant – Help senior citizens during tours and travel. Travel Coordinator – Manage bookings, schedules, and tour arrangements. Customer Support Executive – Assist members through calls and messages. Delivery Support Staff – Help with delivery and service management. Fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Work From Home Form Filling Opportunity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30000.0 - 51000.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2929587</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>We are from VData Tech Madurai having our new process: US Form Filling, available for both single system and bulk systems.We have typing projects which you can able to work at home or office. We will provide image files You have to see the image file and type into the software, Minimum earnings 30k</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>collection executive</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>240000.0 - 300000.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2929586</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>🎯 Role OverviewThe Collection Associate is responsible for managing outstanding customer accounts, ensuring timely collection of payments, and maintaining positive client relationships. This role plays a key part in safeguarding the company’s cash flow and minimizing bad debt.📋 Key ResponsibilitiesC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RFIC Design engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2929585</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3 to 5 years of experience in RF Design EngineeringRF front-end circuit developmentStrong RF circuit design fundamentalsHands-on experience in RF simulation &amp;amp; modelingExperience in RFIC design flow and implementation in parameters such as LNA, PA, Mixer, PLL, and RF SwitchesGood understanding of</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Content Writer Intern</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9000.0 - 10000.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2929584</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Job Description: You will assist our content and marketing team in creating high-quality, engaging, and SEO-friendly content for managed websites&amp;nbsp;and digital platforms. The role involves researching topics, writing and editing content, and optimizing published articles to improve&amp;nbsp;readabili</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Web Consultant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15000.0 - 40000.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2929583</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Job Description:Liberating Solution Pvt. Ltd. is looking for a motivated Web Consultant with experience in outbound calling and client communication. The candidate will be responsible for connecting with potential clients, understanding their digital requirements, and closing deals for website and d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>174000.0 - 194000.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>174000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>194000</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2929219</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Job Responsibilities • Travel to and teach at local villages. • Mobilize (find) new students in areas near the branch so that the branch has 70+ students. • Conduct 4 classes of 1 hour 40 mins daily, each with 18-20 students. • Handle 30 minutes of admin work daily. • Ensure full engagement with FEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Digital Marketing Assitant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2928576</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ob DescriptionYellow Pepper is looking for a Digital Marketing Assistant to support and execute day-to-day digital marketing activities. The role involves managing social media, assisting in ad campaigns, and creating engaging visual content for the brand.Key ResponsibilitiesManage and schedule cont</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>International Customer Sales &amp; Support</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2928575</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>We are looking for a talented International Customer Sales &amp;amp; Support Executive to join our growing telecommunications team. You’ll be the bridge between SMS Consortium and its international partners — ensuring smooth operations, professional communication, and reliable service delivery, while bu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Immigration Consultant</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2928574</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>• Engage in telephonic conversations with prospects and suggest the best immigration/visa options for Canada, Australia (PR Visa), Germany Opportunity Card, Portugal, Sweden, and other European countries.• Oversee all aspects of the Visa and Immigration Services process to ensure smooth and efficien</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Zed Facilitators</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>22500.0 - 35500.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>22500</v>
+      </c>
+      <c r="M12" t="n">
+        <v>35500</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2928572</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>We Are Hiring: ZED FacilitatorWe are looking for a dynamic, knowledgeable, and result-oriented ZED Facilitator to join our team. The ideal candidate will be responsible for guiding, training, and handholding MSMEs through the process of obtaining the ZED (Zero Defect Zero Effect) Certification to en</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100000.0 - 150000.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2926920</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>We are looking for a highly skilled Senior Data Cloud Engineer. This is a remote-first opportunity for professionals who thrive at the intersection of Salesforce Data Cloud, AI, and enterprise data engineering.Role Details:- Experience: 8+ Years- CTC : As per Market&amp;nbsp;- Work Location: 100% Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Documents form fill Data entry work from home csc work</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2926611</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>This is a form filling job from CSC which you can do from your mobile or laptop for which you will also be given training. To do this, only TEC certificate is required. If the candidate does not have it, then the hiring manager will guide you. This is work from home, part time. You have to work only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Catalog Analyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>180000.0 - 300000.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>180000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2925691</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Hi,We have opening for freshers &amp;amp; experienced for Catalog Analyst.Responsibilities:- Upload and manage product listings on various e-commerce platforms.- Ensure accurate and up-to-date product information, including specifications, images, and pricing.- Collaborate with cross-functional teams to</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BD Executive</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200000.0 - 360000.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>360000</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2925499</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1. Identifying opportunities for new business development through following up leads on conducting research on target clients2. Managing the sales process to close new business opportunities3.building strong relationships with the existing portfolio of clients4. collaborating with management on sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Backend associate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15000.0 - 45000.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45000</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2925498</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>We are looking for a Backend Sales Executive who can support the sales team by managing customer data, preparing quotations, processing orders, and coordinating with clients and internal departments. The candidate should have good communication and computer skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bank KYC Executive / KYC Analyst</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15000.0 - 22000.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2925496</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Job SummaryThe KYC Executive is responsible for verifying customer identity, reviewing account opening documents, and ensuring compliance with banking regulations and Anti-Money Laundering (AML) policies. The role helps prevent fraud, financial crime, and unauthorized transactions.Key Responsibiliti</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Trainees as Company Secretary ICSI and Semi-Qualified CS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>7000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2923872</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>We are looking for 3 Trainees for the Company Secretary 21 Months and 2 Semi-Qualified Company Secretaries.Location: Noida (Sector 63 &amp;amp; 2), UP and Delhi (Netaji Subhash Place) Department: Legal &amp;amp; ComplianceEmployment Type: Full-timeQualifications:For Semi-Qualified CS: Completed CS Professio</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Specialist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>18000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>18000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2923871</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Job Title: Talent Acquisition SpecialistLocation: Vadodara, GujaratEmployment Type: Full-time, PermanentImportant Note: This is a night shift role (7:00 PM – 5:00 AM IST).Freshers and recent graduates are encouraged to apply!Role Overview:We’re looking for a dynamic Talent Acquisition Specialist to</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>System Coordinator</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12000.0 - 18000.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M21" t="n">
+        <v>18000</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2923868</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>🚨 Hiring: System Coordinator📍 Location: Muzaffarpur, Bihar🏢 Company: Sri Dhanganga Marble &amp;amp; Tiles(Authorized Kajaria Ceramics Distributor since 1993)We are looking for a responsible and organized System Coordinator to support showroom operations and customer coordination.✨ Key Responsibilities:•</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Computer Operator</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5000.0 - 10000.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2923476</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Work from home. a to z cyber cafe related work karna hai. agar koi problem aati hai to aapko remotely help kiya jayega..</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Social media marketing</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15000.0 - 40000.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2921251</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>About Purple United KidsPurple United Kids is a premium fashion brand dedicated to creating stylish, high-quality apparel and footwear for children. With a focus on comfort, durability, and design, we blend playful creativity with modern trends to empower young personalities to shine. Our collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Business Development Manager &amp; Lead Generation Executive</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2921250</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Dexcom Enterprises is seeking a dynamic and result-oriented Business Development &amp;amp; Lead Generation Executive to drive business growth, build strategic client relationships, and generate qualified leads across domestic and international markets.The role demands a proactive professional who can id</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Academic Counsellors</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>23000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>23000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2921249</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Job description:Senior Academic Counsellor – Job DescriptionLocation: KozhikodeExperience: 3–5 YearsIndustry Preference: EdTechAbout the RoleWe are looking for a dynamic and result-oriented Senior Academic Counsellor to join our team. Theideal candidate should have prior experience in the EdTech ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Academic Counsellors</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>23000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>23000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2921248</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Job description:Senior Academic Counsellor – Job DescriptionLocation: KozhikodeExperience: 3–5 YearsIndustry Preference: EdTechAbout the RoleWe are looking for a dynamic and result-oriented Senior Academic Counsellor to join our team. Theideal candidate should have prior experience in the EdTech ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Medical equipments and Instruments</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2920860</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Promote and sell medical equipment to hospitals and clinics Generate leads and follow up with customers Conduct product presentations and demonstrations Support digital marketing and social media activities Maintain client relationships and achieve sales targets Skills Required Good communication an</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>19900.0 - 37000.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>19900</v>
+      </c>
+      <c r="M28" t="n">
+        <v>37000</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2918955</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Responsible for providing technical support in laboratories, workshops, pilot plants, and research projects. The role involves operation, maintenance, testing, calibration, installation, and repair of scientific instruments, machines, and equipment used in research and development activities. Techni</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mechanical engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>240000.0 - 300000.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>240000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2918376</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Handle mechanical O&amp;M of ZLD/ETP plant equipment. Ensure 24x7 uptime of pumps, blowers, centrifuges, MEE, ATFD, UF/RO skids. Reduce breakdowns &amp; improve efficiency.Plant O&amp;M: Daily monitoring of pumps, gearboxes, blowers, agitators, screw press, centrifuge, MEE, ATFD, RO skids, valves, pipelinesPrev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Digital and Social Media Executive</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12000.0 - 22000.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2916227</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>📢 We’re Hiring | Social Media Executive🏫 Industry: Advertising📍 Location: Bareilly🧑‍💼 Experience: Minimum 2 Years💰 Salary: Up to ₹20,000👩 Eligibility: Only Female Candidates🔑 Key Skills:✔️ Social Media Management (Instagram, Facebook, LinkedIn)✔️ Content Creation &amp;amp; Creative Writing✔️ Reels &amp;amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>16000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2916225</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Urgently hiring for Customer Support ExecutiveAny Graduate and Post Graduate can applyFreshers with strong communication and confidence are welcome to apply.Must own a LaptopStart Day: Immediate JoinersAbout the RoleWe are looking for a dynamic and enthusiastic Customer Support Executive to join our</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2916224</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Urgently hiring for Customer Support ExecutiveAny Graduate and Post Graduate can applyFreshers with strong communication and confidence are welcome to apply.Must own a LaptopStart Day: Immediate JoinersAbout the RoleWe are looking for a dynamic and enthusiastic Customer Support Executive to join our</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>graphics designer cum digital marketing</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10000.0 - 120000.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2915772</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Key Roles &amp; Responsibilities Creative &amp; Graphic Design (50%) Marketing Collateral: Design visually compelling assets including social media posts/carousels, display ads, Google Performance Max creatives, website banners, landing page layouts, and email templates. Brand Identity: Ensure strict adhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Warehouse Executive</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2916974</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Picking products from warehouse racks as per order requirements. Packing items safely and accurately for dispatch. Loading and unloading goods from vehicles and containers. Sorting, scanning, labeling, and organizing inventory. Maintaining cleanliness and safety standards in the warehouse. Ensuring</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Warehouse Associate</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15000.0 - 18000.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>18000</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2917132</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Logistics Executive is responsible for managing dispatch, transportation, inventory tracking, and delivery coordination. Ensures timely shipment, vendor coordination, documentation, and smooth supply chain operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Business Development Intern</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12000.0 - 15000.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2914689</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Inside Sales Intern – Seoak InnovationsLocation: Madhapur, HyderabadDuration: 3 MonthsStipend: ₹15,000/monthRole:Talk to potential customers (calls/messages)Explain services and generate leadsFollow up and help convert leadsRequirements:Good communication skillsImmediate joiners preferredFreshers ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20000.0 - 50000.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2913809</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Connect on : 8454836438 or pcred.rambo@gmail.comJob Description: Business Development ManagerTimings :10am to 7pm (only Sunday off)Salary: depends on the experience1.Develop and implement strategic sales plans to achieve company objectives and revenue targets.2.Identify and pursue new business oppor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25000.0 - 40000.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2913807</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Walls Asia Architects &amp;amp; Engineers is hiring an Architect with 2-3 years of experience for residential and commercial projects in Hyderabad.Roles &amp;amp; Responsibilities:• Prepare architectural concepts and detailed drawings• Work on residential and commercial projects• Coordinate with clients, en</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Instructional Design - Associate Manager</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2000000.0 - 2244000.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2244000</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2913806</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Learning Experience Design &amp;amp; Development – Associate Manager (CL8)We are hiring for the role of Instructional Design – Associate Manager (CL8) for a dynamic and global team environment.Job Details:Role: Learning Experience Design &amp;amp; Development – Associate ManagerLocation: BengaluruCTC: As pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>German Language Expert (HR Operations)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>400000.0 - 800000.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>400000</v>
+      </c>
+      <c r="M40" t="n">
+        <v>800000</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2913805</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Job Title: HR Operations Associates Shift Timings: 1 PM to 11 PM IST.CTC :- As per market&amp;nbsp;Location:- Bengalore Must have skill: Proficient in German Speaking and Writing (B1 / C1+)Good to have skill: HRO Skill Hire to Retire, MS office Shift Timings: 1 PM to 11 PM IST. Should be comfortable wit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Executive - Recruitments</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M41" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2913516</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Seeking an Executive - Recruitments to manage end-to-end hiring processes for consultancy clients, ensuring top talent acquisition. Responsibilities include sourcing, screening, scheduling interviews, and coordinating with clients to fulfill recruitment needs efficiently. Requirements: Bachelor’s de</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>"Inside sales Representative required @Gurgaon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>250000.0 - 350000.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>350000</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2909606</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>- Job Description:&amp;nbsp; &amp;nbsp; - Drive walk-ins from inbound leads&amp;nbsp; &amp;nbsp; - Pre-qualify, counsel, and convert leads&amp;nbsp; &amp;nbsp; - Call inbound leads using LeadSquared CRM&amp;nbsp; &amp;nbsp; - Counsel prospects on Emversity programmes&amp;nbsp; &amp;nbsp; - Book and drive physical walk-in demos- Requiremen</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>16000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2909605</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Easy Settlement, is a leading provider of financial and legal services specializing in loan settlement and debt resolution. Our mission is to assist individuals and businesses burdened by personal loans, credit card debts, and EMI challenges by offering customized solutions.With a dedicated team of</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Digital and Social Media Executive</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M44" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2909602</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Job Title: Social Media Executive**Location: Mumbai**Experience:** 1+ Years**Industry:** PR Agency### Job DescriptionWe are looking for a creative and proactive Social Media Executive to join our team in Mumbai. The ideal candidate should have hands-on experience in managing social media platforms,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>customer service executive</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>240000.0 - 300000.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="M45" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2909601</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Customer Support Executive (Voice &amp;amp; Email Process) – English, Hindi &amp;amp; Any Native LanguageWe’re looking for candidates with 1–2 years of experience in customer support, preferably in voice Bpo, who are strong in customer service skills and delivering great customer experiences.🔧 Responsibilit</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Customer Support Executive</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2909599</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>We’re Hiring: Customer Support Executive – International (Voice &amp;amp; Chat)Location: KolkataShifts: Rotational (Day/Night)Experience: 1–3 YearsDepartment: Customer Support / Operations________________________________________Job Summary:We are looking for dynamic professionals to join our Internation</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Customer Success Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300000.0 - 500000.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M47" t="n">
+        <v>500000</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2909598</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Location : Bangalore, Mumbai, Ahmedabad🕐 Notice Period : Immediate Joiners Preferred👤 Role : Customer Success Consultant ( Freshers can also apply)🎓 Education : Any Graduate / Post Graduate🛠️ Skills We’re Looking For:- Business Development- Lead Generation through Channel partners- Customer Success-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sales Administration and Commercial Officer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>400000.0 - 600000.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>400000</v>
+      </c>
+      <c r="M48" t="n">
+        <v>600000</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2906366</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Administrative support for Project Sales Team, Advanced MS Excel, SAP tool, Accounting and Taxation knowledge, Reporting skills, Vendor management, Commercial knowledge. Accurate dealer level sales reports as per requirement. Logistics and operational support to Unit level initiatives.Employee life</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Project Technical Support-III</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2906121</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Project entitled-: “Equitable, Quality universal health coverage Implementation research Project for optimizing comprehensive primary health care through Health and Wellness Centres in Primpri Chinchwad Municipal Corporation, Pune district of Maharashtra- EQUIP-HWCs” funded by Indian Council of Medi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SUPER DISTRIBUTER</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2897498</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Seeking a Super Distributor to drive monthly sales targets by managing and coordinating team efforts across master distributors and distributors. Responsibilities: Achieve monthly sales targets through effective team leadership. Monitor distributor performance and ensure alignment with goals. Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Business developement</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2894026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>LIC is hiring for Insurance policy advisor across India become certified LIC advisor and earn good monthly income</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BANKING JOB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>21000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M52" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2545046</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Join this group:- https://chat.whatsapp.com/BlZcHvLh57v0EmygqAT4HF?mode=gi_t 🏦 BANKING CAREER OPPORTUNITY - MAHARASHTRA 🏦 We are hiring for Equitas Small Finance Bank and Kotak Mahindra Bank (NextGen Program). Join one of India's fastest-growing banking sectors! 📅 Online Interview Schedule Process:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Assembly technician</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150000.0 - 240000.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M53" t="n">
+        <v>240000</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2889551</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>We are looking for assembly specialists, who can also quality check the spare parts coming in from suppliers, for wheelchair fitting. Also automotive wire joining work. Check our products page on website to understand. Technician must also know how to solder. Other skills required include: 1. using</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>pest control operator</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10000.0 - 12000.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M54" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2885420</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>hotel , hospital. college fild work , no target based job, location raipur chhattisgarh .acomodation free</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TECHNICIAN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2884256</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>TECHNICIAN IN REFIGIRATION AND ABLE TO INSTALL AC AND REFIGIRATORS IN ALL INDIA LEVEL AND COMPLETE WORK OF REFIGIRATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CARPENTER</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>300000.0 - 800000.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M56" t="n">
+        <v>800000</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2884212</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>field and warehouse comfortable Carpenter plywood work and wood work pvc work door work everything aembly and repair in furniture product</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LIC Agent</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2884151</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Candidate will be selling insurance products Providing after sales services to the customers Market research of the organisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LIC Agent</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2880927</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Candidate will be selling insurance products Providing after sales services to the customers Market research of the organisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>25000.0 - 40000.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M59" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2871625</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Seeking a Construction Electrician to install, repair, and maintain electrical systems in construction projects. Full-time role. Responsibilities include wiring, troubleshooting, reading blueprints, and ensuring compliance with safety standards. Requirements: 0-2 years of experience, basic electrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Warehouse Associate</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15000.0 - 20000.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M60" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2861480</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Logistics Executive is responsible for managing dispatch, transportation, inventory tracking, and delivery coordination. Ensures timely shipment, vendor coordination, documentation, and smooth supply chain operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>insurance policy advisor</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2861502</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>SBI is hiring for Insurance policy advisor across India become certified SBi Insurance advisor and earn good monthly income</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Delivery Rider</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M62" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2849769</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>We are hiring delivery riders for India’s biggest quick commerce company across the country. This is a great opportunity to earn ₹25,000 to ₹40,000 per month. All you need is a bike, the excitement to work hard, and the ambition to become financially independent. Work just 8–9 hours daily, and be pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Life Mitra</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2848567</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>A Life Mitra is a commissioned insurance advisor role at SBI Life Insurance that involves identifying customer needs, recommending appropriate insurance products, and building long-term relationships to help clients secure their financial futures. This role offers flexible, full-time or part-time wo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PWD Deaf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>18000.0 - 22000.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>18000</v>
+      </c>
+      <c r="M64" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2846129</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Amazon PNQ3 – Free Job Opportunity (pwd deaf ) Tomorrow Interview &amp; Sat Joining. 🚹🚺 Male &amp; Female Candidates Welcome 🗓️ Interview Details: ⏰ Time: 08:30 AM 💼 Job Role: * Picking * Packing * Scanning 💰 Salary Structure: * Basic Salary: ₹15,921 * Night Shift Allowance: ₹1,150 * Attendance Bonus: ₹2,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Executive Trainee (I&amp;FS and Physics Disciplines)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>76499.0 - 76500.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>76499</v>
+      </c>
+      <c r="M65" t="n">
+        <v>76500</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2039335</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Nuclear Power Corporation of India Limited, A Central Public Sector Enterprise, under Administrative Control of Department of Atomic Energy, Government of India invites online applications for 30 vacancies for the post of Executive Trainee in Industrial &amp; Fire Safety Discipline and Physics Disciplin</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Business Associates</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2757987</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>We are onboarding Business Associates (Agents) with Shriram Finance Limited. Products to Sell: • Fixed Deposits • Life Insurance • Health Insurance • Vehicle Insurance • Mutual Funds Benefits: • Commission on every policy &amp; investment • No joining fees • No exam • Agent code generated within 1 day •</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Home Healthcare</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20000.0 - 30000.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M67" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2668334</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Responsibilities: * Provide patient care with empathy &amp; expertise * Collaborate with healthcare team on treatment plans * Administer medications, monitor vital signs, document findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Warehouse associate</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>15000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M68" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2656236</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Seeking a Warehouse Associate to support daily logistics operations in a fast-paced environment. This is a freelance role. Responsibilities include picking, loading, and assisting with warehouse tasks, ensuring timely and accurate order fulfillment. No prior experience required. Must be physically f</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Warehouse Associate</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>16000.0 - 25000.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M69" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2654746</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>* Pick, pack and scan customer orders accurately * Maintain proper inventory and stock records * Use handheld scanners and warehouse systems * Ensure timely dispatch of orders * Follow safety guidelines and company policies * Load and unload goods when required * Maintain cleanliness and organizatio</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Packing , Scanning ,Loading , Unloading</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12592.0 - 16779.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>12592</v>
+      </c>
+      <c r="M70" t="n">
+        <v>16779</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2651619</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>*Hiring In Amazon Full Time &amp; Part TIme* ➡️Profile - Picking - Packing , Loading - Unloading *💸Delhi PT Salary - 12592 + PF +ESIC* • Insentives • Attendance Bonus *Part Time 5 Hours Work Rotational Shift* 📍Location :- •Delhi NCR ➡️Required Documents •Aadhar Card •Bank Passbook •Email id •Mobile No •</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>250000.0 - 275000.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M71" t="n">
+        <v>275000</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2648789</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Designation Warehouse Associate Role Pick Pack Stow Re-bin Loading/Unloading Job Type Physical: Standing/Walking Job Note: Associates are expected to walk and stand for 9 hrs. Shift Timings Dayshift 8:45am to 6:45pm Night Shift: 6:45pm to 4:45am Note: Two-week day and Two-week Night Working Days 5 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2627142</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>This is a full-time role for an Architect/Engineer, based in Ahmedabad with sites across western India. The Architect will be responsible for planning, designing, and overseeing the implementation of architectural projects. Key responsibilities include creating architectural designs, collaborating w</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2582059</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>SkyTech Digital Labs is offering a Software Developer Internship for students interested in gaining practical experience in web development and modern technologies. This internship focuses on learning, project-based development, and improving technical skills in a collaborative environment. Location</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/ncs.xlsx
+++ b/output/ncs.xlsx
@@ -429,10 +429,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -442,7 +442,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
@@ -546,14 +546,18 @@
           <t>Senior Citizen Tour pan India</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SHANTI SENIOR CITIZEN SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -585,7 +589,11 @@
         <v>1500000</v>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-05-26T05:34:21.193784Z</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2930777</t>
@@ -608,14 +616,22 @@
           <t>Work From Home Form Filling Opportunity</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bengaluru Urban, Karnataka, Chennai, Tamil Nadu, Hyderabad, Telangana</t>
+        </is>
+      </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -647,7 +663,11 @@
         <v>51000</v>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:25:07.055Z</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2929587</t>
@@ -670,14 +690,22 @@
           <t>collection executive</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -709,7 +737,11 @@
         <v>300000</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:25:07.033359Z</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2929586</t>
@@ -732,14 +764,22 @@
           <t>RFIC Design engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Karnataka, Nagpur, Maharashtra</t>
+        </is>
+      </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -771,7 +811,11 @@
         <v>30000</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:25:07.010524Z</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2929585</t>
@@ -794,14 +838,22 @@
           <t>Content Writer Intern</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -833,7 +885,11 @@
         <v>10000</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:25:06.988939Z</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2929584</t>
@@ -856,14 +912,22 @@
           <t>Web Consultant</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kolkata, West Bengal</t>
+        </is>
+      </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -895,7 +959,11 @@
         <v>40000</v>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:25:06.946647Z</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2929583</t>
@@ -918,14 +986,22 @@
           <t>Teacher</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AAM Foundation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chitrakoot Dham, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -957,7 +1033,11 @@
         <v>194000</v>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-05-25T09:36:13.340673Z</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2929219</t>
@@ -980,14 +1060,22 @@
           <t>Digital Marketing Assitant</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sonipat, Haryana</t>
+        </is>
+      </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1019,7 +1107,11 @@
         <v>20000</v>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-05-24T18:25:40.249742Z</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2928576</t>
@@ -1042,14 +1134,22 @@
           <t>International Customer Sales &amp; Support</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kolkata, West Bengal</t>
+        </is>
+      </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1081,7 +1181,11 @@
         <v>25000</v>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-05-24T18:25:40.232494Z</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2928575</t>
@@ -1104,14 +1208,22 @@
           <t>Immigration Consultant</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New Delhi, Delhi</t>
+        </is>
+      </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1143,7 +1255,11 @@
         <v>25000</v>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-05-24T18:25:40.212497Z</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2928574</t>
@@ -1166,14 +1282,22 @@
           <t>Zed Facilitators</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thane, Maharashtra</t>
+        </is>
+      </c>
       <c r="D12" t="b">
         <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1205,7 +1329,11 @@
         <v>35500</v>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-05-24T18:25:40.157474Z</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2928572</t>
@@ -1228,14 +1356,22 @@
           <t>Senior Data Cloud Engineer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1267,7 +1403,11 @@
         <v>150000</v>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-05-23T18:25:06.969873Z</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2926920</t>
@@ -1290,14 +1430,18 @@
           <t>Documents form fill Data entry work from home csc work</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VISHAL PRADIP SATTE</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1329,7 +1473,11 @@
         <v>1500000</v>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-05-23T00:50:15.815302Z</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2926611</t>
@@ -1352,14 +1500,22 @@
           <t>Catalog Analyst</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1391,7 +1547,11 @@
         <v>300000</v>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-05-22T18:25:06.144892Z</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2925691</t>
@@ -1414,14 +1574,22 @@
           <t>BD Executive</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="D16" t="b">
         <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1453,7 +1621,11 @@
         <v>360000</v>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-05-22T15:17:35.857847Z</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2925499</t>
@@ -1476,14 +1648,22 @@
           <t>Backend associate</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1515,7 +1695,11 @@
         <v>45000</v>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-05-22T15:17:35.836151Z</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2925498</t>
@@ -1538,14 +1722,18 @@
           <t>Bank KYC Executive / KYC Analyst</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1577,7 +1765,11 @@
         <v>22000</v>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-05-22T15:17:35.788771Z</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2925496</t>
@@ -1600,14 +1792,22 @@
           <t>Trainees as Company Secretary ICSI and Semi-Qualified CS</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Delhi, New Delhi, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1639,7 +1839,11 @@
         <v>30000</v>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-05-21T18:25:06.811923Z</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2923872</t>
@@ -1662,14 +1866,22 @@
           <t>Talent Acquisition Specialist</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vadodara, Gujarat</t>
+        </is>
+      </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1701,7 +1913,11 @@
         <v>20000</v>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-05-21T18:25:06.784672Z</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2923871</t>
@@ -1724,14 +1940,22 @@
           <t>System Coordinator</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Muzaffarpur, Bihar</t>
+        </is>
+      </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1763,7 +1987,11 @@
         <v>18000</v>
       </c>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-05-21T18:25:06.706169Z</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2923868</t>
@@ -1786,14 +2014,22 @@
           <t>Computer Operator</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Shivanshu Cafe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Gaya, Bihar</t>
+        </is>
+      </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1825,7 +2061,11 @@
         <v>10000</v>
       </c>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-05-21T09:18:06.984993Z</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2923476</t>
@@ -1848,14 +2088,22 @@
           <t>Social media marketing</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D23" t="b">
         <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1887,7 +2135,11 @@
         <v>40000</v>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-05-20T18:25:06.344443Z</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2921251</t>
@@ -1910,14 +2162,22 @@
           <t>Business Development Manager &amp; Lead Generation Executive</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D24" t="b">
         <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1949,7 +2209,11 @@
         <v>25000</v>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-05-20T18:25:06.3259Z</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2921250</t>
@@ -1972,14 +2236,22 @@
           <t>Senior Academic Counsellors</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kozhikode, Kerala</t>
+        </is>
+      </c>
       <c r="D25" t="b">
         <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2011,7 +2283,11 @@
         <v>30000</v>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-05-20T18:25:06.304069Z</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2921249</t>
@@ -2034,14 +2310,22 @@
           <t>Senior Academic Counsellors</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kozhikode, Kerala</t>
+        </is>
+      </c>
       <c r="D26" t="b">
         <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2073,7 +2357,11 @@
         <v>30000</v>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-05-20T18:25:06.274153Z</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2921248</t>
@@ -2096,14 +2384,22 @@
           <t>Medical equipments and Instruments</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SHANTI SENIOR CITIZEN SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Himatnagar, Gujarat</t>
+        </is>
+      </c>
       <c r="D27" t="b">
         <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2135,7 +2431,11 @@
         <v>1500000</v>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-05-20T11:32:42.552273Z</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2920860</t>
@@ -2158,14 +2458,18 @@
           <t>Technician</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CSIR-CIMFR</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="b">
         <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2197,7 +2501,11 @@
         <v>37000</v>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-19T20:30:25.680102Z</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2918955</t>
@@ -2220,14 +2528,18 @@
           <t>Mechanical engineer</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IWTRS PVT LTD</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="b">
         <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2259,7 +2571,11 @@
         <v>300000</v>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-19T11:45:09.42416Z</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2918376</t>
@@ -2282,14 +2598,22 @@
           <t>Digital and Social Media Executive</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bareilly, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D30" t="b">
         <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2321,7 +2645,11 @@
         <v>22000</v>
       </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-18T18:25:06.20301Z</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2916227</t>
@@ -2344,14 +2672,22 @@
           <t>Customer Support Executive</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Delhi, New Delhi, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D31" t="b">
         <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2383,7 +2719,11 @@
         <v>20000</v>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-18T18:25:06.166363Z</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2916225</t>
@@ -2406,14 +2746,22 @@
           <t>Customer Support Executive</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Delhi, Uttar Pradesh, New Delhi</t>
+        </is>
+      </c>
       <c r="D32" t="b">
         <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2445,7 +2793,11 @@
         <v>20000</v>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-05-18T18:25:06.132147Z</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2916224</t>
@@ -2468,14 +2820,22 @@
           <t>graphics designer cum digital marketing</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mindpik Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Kolkata, West Bengal, Bidhannagar</t>
+        </is>
+      </c>
       <c r="D33" t="b">
         <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2507,7 +2867,11 @@
         <v>120000</v>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:50:02.30652Z</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2915772</t>
@@ -2530,14 +2894,22 @@
           <t>Warehouse Executive</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AASAANJOBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>achhanpur b.o, HARYANA</t>
+        </is>
+      </c>
       <c r="D34" t="b">
         <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2561,7 +2933,11 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-05-18T20:30:29.926572Z</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2916974</t>
@@ -2584,14 +2960,18 @@
           <t>Warehouse Associate</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AASAANJOBS PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="b">
         <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2623,7 +3003,11 @@
         <v>18000</v>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-05-18T20:30:32.416775Z</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2917132</t>
@@ -2646,14 +3030,22 @@
           <t>Business Development Intern</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana</t>
+        </is>
+      </c>
       <c r="D36" t="b">
         <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2685,7 +3077,11 @@
         <v>15000</v>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-05-17T18:25:42.377003Z</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2914689</t>
@@ -2708,14 +3104,22 @@
           <t>Business Development Manager</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra</t>
+        </is>
+      </c>
       <c r="D37" t="b">
         <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2747,7 +3151,11 @@
         <v>50000</v>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-05-16T18:25:08.185879Z</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2913809</t>
@@ -2770,14 +3178,22 @@
           <t>Architect</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana</t>
+        </is>
+      </c>
       <c r="D38" t="b">
         <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2809,7 +3225,11 @@
         <v>40000</v>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-05-16T18:25:08.146525Z</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2913807</t>
@@ -2832,14 +3252,22 @@
           <t>Instructional Design - Associate Manager</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bengaluru Urban, Karnataka</t>
+        </is>
+      </c>
       <c r="D39" t="b">
         <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2871,7 +3299,11 @@
         <v>2244000</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-05-16T18:25:08.126335Z</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2913806</t>
@@ -2894,14 +3326,22 @@
           <t>German Language Expert (HR Operations)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bengaluru Urban, Karnataka</t>
+        </is>
+      </c>
       <c r="D40" t="b">
         <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2933,7 +3373,11 @@
         <v>800000</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-05-16T18:25:08.084884Z</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2913805</t>
@@ -2956,14 +3400,22 @@
           <t>Executive - Recruitments</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kapgrow Corporate Advisory Services Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
       <c r="D41" t="b">
         <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2995,7 +3447,11 @@
         <v>30000</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-05-16T11:37:31.718883Z</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2913516</t>
@@ -3018,14 +3474,22 @@
           <t>"Inside sales Representative required @Gurgaon</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Karnataka, Haryana, Pune, Maharashtra</t>
+        </is>
+      </c>
       <c r="D42" t="b">
         <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3057,7 +3521,11 @@
         <v>350000</v>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-05-14T14:31:11.021104Z</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2909606</t>
@@ -3080,14 +3548,22 @@
           <t>Customer Support Executive</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D43" t="b">
         <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3119,7 +3595,11 @@
         <v>20000</v>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-05-14T14:30:17.177719Z</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2909605</t>
@@ -3142,14 +3622,22 @@
           <t>Digital and Social Media Executive</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
       <c r="D44" t="b">
         <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3181,7 +3669,11 @@
         <v>30000</v>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:48:53.46389Z</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2909602</t>
@@ -3204,14 +3696,22 @@
           <t>customer service executive</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
       <c r="D45" t="b">
         <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3243,7 +3743,11 @@
         <v>300000</v>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:48:53.424425Z</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2909601</t>
@@ -3266,14 +3770,22 @@
           <t>Customer Support Executive</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
       <c r="D46" t="b">
         <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3305,7 +3817,11 @@
         <v>20000</v>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:37:48.678673Z</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2909599</t>
@@ -3328,14 +3844,22 @@
           <t>Customer Success Consultant</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
       <c r="D47" t="b">
         <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3367,7 +3891,11 @@
         <v>500000</v>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-05-14T13:37:48.636747Z</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2909598</t>
@@ -3390,14 +3918,18 @@
           <t>Sales Administration and Commercial Officer</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Saira People Tech Solutions Private Limited</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="b">
         <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3429,7 +3961,11 @@
         <v>600000</v>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-05-13T12:11:40.495052Z</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2906366</t>
@@ -3452,14 +3988,18 @@
           <t>Project Technical Support-III</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>E-SOLUTIONS IT SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="b">
         <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3491,7 +4031,11 @@
         <v>1500000</v>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-05-13T04:54:40.415881Z</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2906121</t>
@@ -3514,14 +4058,18 @@
           <t>SUPER DISTRIBUTER</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PARTHA SARATHI SERVICES (OPC) PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="b">
         <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3553,7 +4101,11 @@
         <v>1500000</v>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-05-08T10:01:45.831929Z</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2897498</t>
@@ -3576,14 +4128,22 @@
           <t>Business developement</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nashik, MAHARASHTRA</t>
+        </is>
+      </c>
       <c r="D51" t="b">
         <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3607,7 +4167,11 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-05-06T20:30:35.342283Z</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2894026</t>
@@ -3630,14 +4194,18 @@
           <t>BANKING JOB</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>banking career solution latur,training and placeme</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="b">
         <v>0</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3669,7 +4237,11 @@
         <v>25000</v>
       </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-05-06T08:30:10.279413Z</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2545046</t>
@@ -3692,14 +4264,22 @@
           <t>Assembly technician</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Caruna mobility</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ganapathichettikulam, Puducherry</t>
+        </is>
+      </c>
       <c r="D53" t="b">
         <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3731,7 +4311,11 @@
         <v>240000</v>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-05-05T05:15:17.459479Z</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2889551</t>
@@ -3754,14 +4338,18 @@
           <t>pest control operator</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HERBS VECTOR MANAGMENT SERVICES</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="b">
         <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3793,7 +4381,11 @@
         <v>12000</v>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-05-02T19:07:09.301249Z</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2885420</t>
@@ -3816,14 +4408,18 @@
           <t>TECHNICIAN</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MAHAKALI TRADERS</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="b">
         <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3855,7 +4451,11 @@
         <v>1500000</v>
       </c>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-05-01T16:48:09.182415Z</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2884256</t>
@@ -3878,14 +4478,18 @@
           <t>CARPENTER</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RS HR</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="b">
         <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3917,7 +4521,11 @@
         <v>800000</v>
       </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-05-01T03:20:30.801545Z</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2884212</t>
@@ -3940,14 +4548,22 @@
           <t>LIC Agent</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LIC OF INDIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>new delhi, DELHI</t>
+        </is>
+      </c>
       <c r="D57" t="b">
         <v>0</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3971,7 +4587,11 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-04-30T20:31:04.037493Z</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2884151</t>
@@ -3994,14 +4614,22 @@
           <t>LIC Agent</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LIC OF INDIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>new delhi, DELHI</t>
+        </is>
+      </c>
       <c r="D58" t="b">
         <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4025,7 +4653,11 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-04-28T20:31:01.0592Z</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2880927</t>
@@ -4048,14 +4680,18 @@
           <t>Electrician</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PRERNA CONSULTANCY</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="b">
         <v>0</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4087,7 +4723,11 @@
         <v>40000</v>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-04-23T08:45:18.554261Z</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2871625</t>
@@ -4110,14 +4750,22 @@
           <t>Warehouse Associate</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AASAANJOBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>abbaiahnahalli b.o, KARNATAKA</t>
+        </is>
+      </c>
       <c r="D60" t="b">
         <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4149,7 +4797,11 @@
         <v>20000</v>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-04-16T20:30:04.26Z</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2861480</t>
@@ -4172,14 +4824,22 @@
           <t>insurance policy advisor</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nashik, MAHARASHTRA</t>
+        </is>
+      </c>
       <c r="D61" t="b">
         <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4203,7 +4863,11 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-04-16T20:30:04.915051Z</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2861502</t>
@@ -4226,14 +4890,18 @@
           <t>Delivery Rider</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SHREE ENTERPRISE</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="b">
         <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4265,7 +4933,11 @@
         <v>25000</v>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-04-10T17:22:26.842635Z</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2849769</t>
@@ -4288,14 +4960,18 @@
           <t>Life Mitra</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SBI LIFE INSURANCE COMPANY LIMITED</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="b">
         <v>0</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4327,7 +5003,11 @@
         <v>1500000</v>
       </c>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-04-09T09:09:11.601871Z</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2848567</t>
@@ -4350,14 +5030,18 @@
           <t>PWD Deaf</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Amazoon.in</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="b">
         <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4389,7 +5073,11 @@
         <v>22000</v>
       </c>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-04-08T12:05:09.801657Z</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2846129</t>
@@ -4412,14 +5100,18 @@
           <t>Executive Trainee (I&amp;FS and Physics Disciplines)</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nuclear Power Corporation of India Ltd</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="b">
         <v>0</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4451,7 +5143,11 @@
         <v>76500</v>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-04-07T09:37:09.959324Z</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2039335</t>
@@ -4474,14 +5170,22 @@
           <t>Business Associates</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SHRIRAM FINANCE LIMITED</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana</t>
+        </is>
+      </c>
       <c r="D66" t="b">
         <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4513,7 +5217,11 @@
         <v>1500000</v>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-03-28T14:50:09.654739Z</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2757987</t>
@@ -4536,14 +5244,18 @@
           <t>Home Healthcare</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Curagers Healthcare</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="b">
         <v>0</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4575,7 +5287,11 @@
         <v>30000</v>
       </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:52:01.911168Z</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2668334</t>
@@ -4598,14 +5314,18 @@
           <t>Warehouse associate</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Amazoon.in</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="b">
         <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4637,7 +5357,11 @@
         <v>25000</v>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-03-22T02:00:39.688671Z</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2656236</t>
@@ -4660,14 +5384,18 @@
           <t>Warehouse Associate</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Amazoon.in</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="b">
         <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4699,7 +5427,11 @@
         <v>25000</v>
       </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-03-21T04:48:54.464785Z</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2654746</t>
@@ -4722,14 +5454,18 @@
           <t>Packing , Scanning ,Loading , Unloading</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SUNRISING STAFFING SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="b">
         <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4761,7 +5497,11 @@
         <v>16779</v>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-03-19T10:18:03.053257Z</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2651619</t>
@@ -4784,14 +5524,18 @@
           <t>WAREHOUSE ASSOCIATE</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>INTEXLOGISTICS INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="b">
         <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4823,7 +5567,11 @@
         <v>275000</v>
       </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-03-18T07:31:17.432238Z</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2648789</t>
@@ -4846,14 +5594,22 @@
           <t>Architect</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Poonam Ashish Trambadia Conservation Architects</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat</t>
+        </is>
+      </c>
       <c r="D72" t="b">
         <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4885,7 +5641,11 @@
         <v>1500000</v>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-03-16T09:26:28.9623Z</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2627142</t>
@@ -4908,14 +5668,18 @@
           <t>Software Developer Intern</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SkyTech Digital Labs</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="b">
         <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4947,7 +5711,11 @@
         <v>1500000</v>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-03-12T17:39:47.966864Z</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2582059</t>

--- a/output/ncs.xlsx
+++ b/output/ncs.xlsx
@@ -425,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -543,12 +543,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Citizen Tour pan India</t>
+          <t>Delivery Boy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHANTI SENIOR CITIZEN SERVICES PRIVATE LIMITED</t>
+          <t>Sr Fast Connect Staffing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -557,7 +557,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -577,26 +577,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>426000.0 - 480000.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>15000</v>
+        <v>426000</v>
       </c>
       <c r="M2" t="n">
-        <v>1500000</v>
+        <v>480000</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-26T05:34:21.193784Z</t>
+          <t>2026-06-07T04:32:49.79416Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2930777</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2944926</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,14 +606,14 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>English Senior Citizen Tour Assistant – Help senior citizens during tours and travel. Travel Coordinator – Manage bookings, schedules, and tour arrangements. Customer Support Executive – Assist members through calls and messages. Delivery Support Staff – Help with delivery and service management. Fr</t>
+          <t>We are hiring Delivery Executives for leading delivery platforms such as Zepto, Blinkit, Swiggy, Zomato, and Porter. Responsibilities: Deliver food, grocery, and parcel orders to customers. Ensure timely and safe delivery. Follow company guidelines and delivery procedures. Maintain professional beha</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Work From Home Form Filling Opportunity</t>
+          <t>Sr. Executive - Sales</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bengaluru Urban, Karnataka, Chennai, Tamil Nadu, Hyderabad, Telangana</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -651,26 +651,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30000.0 - 51000.0</t>
+          <t>200000.0 - 500000.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>30000</v>
+        <v>200000</v>
       </c>
       <c r="M3" t="n">
-        <v>51000</v>
+        <v>500000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-25T18:25:07.055Z</t>
+          <t>2026-06-06T18:25:06.691921Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2929587</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2944625</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -680,24 +680,24 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>We are from VData Tech Madurai having our new process: US Form Filling, available for both single system and bulk systems.We have typing projects which you can able to work at home or office. We will provide image files You have to see the image file and type into the software, Minimum earnings 30k</t>
+          <t>JOB TITLE: Sales and Marketing Manager [ Building Materials]CONTACT NO: 9099166000Job Summary:A Sales and Marketing Manager in the building materials industry is responsible for increasing product sales, developing market presence, managing customer relationships, and achieving revenue targets.Key R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>collection executive</t>
+          <t>Hospital and Home Cleaner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>SHANTI SENIOR CITIZEN SERVICES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Nashik, Maharashtra, Mumbai, Mahesana, Gujarat, Himatnagar, Bhopal, Madhya Pradesh, Thiruvananthapuram, Kerala</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -725,26 +725,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>240000.0 - 300000.0</t>
+          <t>15000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>240000</v>
+        <v>15000</v>
       </c>
       <c r="M4" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-25T18:25:07.033359Z</t>
+          <t>2026-06-06T06:14:33.59597Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2929586</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943785</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -754,26 +754,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>🎯 Role OverviewThe Collection Associate is responsible for managing outstanding customer accounts, ensuring timely collection of payments, and maintaining positive client relationships. This role plays a key part in safeguarding the company’s cash flow and minimizing bad debt.📋 Key ResponsibilitiesC</t>
+          <t>English (Short) Hospital / Home / Domestic Cleaner (Deaf &amp; Speech Impaired) Clean rooms, wards, bathrooms, kitchens, and common areas. Sweep, mop, dust, wash, and sanitize surfaces. Collect and dispose of waste properly. Follow hygiene, safety, and infection-control rules. Use cleaning equipment saf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RFIC Design engineer</t>
+          <t>House Keeping Helper -Deaf and Speech Impaired</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Karnataka, Nagpur, Maharashtra</t>
-        </is>
-      </c>
+          <t>SHANTI SENIOR CITIZEN SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="b">
         <v>0</v>
       </c>
@@ -799,26 +795,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25000.0 - 30000.0</t>
+          <t>13500.0 - 162000.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>25000</v>
+        <v>13500</v>
       </c>
       <c r="M5" t="n">
-        <v>30000</v>
+        <v>162000</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-25T18:25:07.010524Z</t>
+          <t>2026-06-06T05:08:43.843392Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2929585</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943756</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -828,14 +824,14 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3 to 5 years of experience in RF Design EngineeringRF front-end circuit developmentStrong RF circuit design fundamentalsHands-on experience in RF simulation &amp;amp; modelingExperience in RFIC design flow and implementation in parameters such as LNA, PA, Mixer, PLL, and RF SwitchesGood understanding of</t>
+          <t>ગુજરાતી હાઉસકીપિંગ સ્ટાફ – મલ્ટી સ્પેશિયાલિટી હોસ્પિટલ વોર્ડ, ICU, OPD, રૂમ અને વોશરૂમની સફાઈ જાળવવી. હોસ્પિટલની સ્વચ્છતા અને ઇન્ફેક્શન કંટ્રોલના નિયમોનું પાલન કરવું. કચરાનો યોગ્ય નિકાલ કરવો. શિફ્ટ મુજબ કામ કરવું. हिन्दी हाउसकीपिंग स्टाफ – मल्टी स्पेशियलिटी हॉस्पिटल वार्ड, ICU, OPD, कमरों और शौचालयो</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Content Writer Intern</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -845,7 +841,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -873,26 +869,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9000.0 - 10000.0</t>
+          <t>60000.0 - 70000.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>9000</v>
+        <v>60000</v>
       </c>
       <c r="M6" t="n">
-        <v>10000</v>
+        <v>70000</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-25T18:25:06.988939Z</t>
+          <t>2026-06-05T18:25:06.241264Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2929584</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943192</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -902,14 +898,14 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Job Description: You will assist our content and marketing team in creating high-quality, engaging, and SEO-friendly content for managed websites&amp;nbsp;and digital platforms. The role involves researching topics, writing and editing content, and optimizing published articles to improve&amp;nbsp;readabili</t>
+          <t>Operations ManagerLocation: Chennai – Shenoy NagarExperience: 5–8 YearsSalary: As per NormsAvailability: Immediate joinersLanguage: Fluent Hindi (Mandatory)Key Responsibilities: Manage and oversee operations of the organization Develop and implement operational strategies and processes Monitor pe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Web Consultant</t>
+          <t>Client Servicing Representative</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -919,7 +915,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -947,26 +943,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15000.0 - 40000.0</t>
+          <t>20000.0 - 27000.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="M7" t="n">
-        <v>40000</v>
+        <v>27000</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-25T18:25:06.946647Z</t>
+          <t>2026-06-05T18:25:06.221012Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2929583</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943191</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -976,24 +972,24 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Job Description:Liberating Solution Pvt. Ltd. is looking for a motivated Web Consultant with experience in outbound calling and client communication. The candidate will be responsible for connecting with potential clients, understanding their digital requirements, and closing deals for website and d</t>
+          <t>Position OverviewWe are seeking a proactive, customer-focused, and relationship-driven professional to join our team as a Client Servicing Representative. The role involves managing client relationships, ensuring exceptional service delivery, resolving customer concerns, and maintaining a seamless c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Corporate Sales Manager</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AAM Foundation</t>
+          <t>Vee technologies pvt ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chitrakoot Dham, Uttar Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -1021,26 +1017,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>174000.0 - 194000.0</t>
+          <t>400000.0 - 600000.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>174000</v>
+        <v>400000</v>
       </c>
       <c r="M8" t="n">
-        <v>194000</v>
+        <v>600000</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-25T09:36:13.340673Z</t>
+          <t>2026-06-05T18:25:06.184881Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2929219</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943190</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1050,14 +1046,14 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Job Responsibilities • Travel to and teach at local villages. • Mobilize (find) new students in areas near the branch so that the branch has 70+ students. • Conduct 4 classes of 1 hour 40 mins daily, each with 18-20 students. • Handle 30 minutes of admin work daily. • Ensure full engagement with FEA</t>
+          <t>Geotrackers,&amp;nbsp;is hiring self motivated, result oriented professionals, with a flair for technology and loads of self-confidence, for the role of&amp;nbsp;Corporate Sales Manager/BDM.Job descriptionKRAs :Own, manage and drive sales in the Corporate &amp;amp; B2B segment in the stateCustomer consultatio</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Digital Marketing Assitant</t>
+          <t>Corporate Sales Manager</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1067,7 +1063,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sonipat, Haryana</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -1095,26 +1091,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15000.0 - 20000.0</t>
+          <t>400000.0 - 600000.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>15000</v>
+        <v>400000</v>
       </c>
       <c r="M9" t="n">
-        <v>20000</v>
+        <v>600000</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24T18:25:40.249742Z</t>
+          <t>2026-06-05T18:25:06.162074Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2928576</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943189</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1124,14 +1120,14 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ob DescriptionYellow Pepper is looking for a Digital Marketing Assistant to support and execute day-to-day digital marketing activities. The role involves managing social media, assisting in ad campaigns, and creating engaging visual content for the brand.Key ResponsibilitiesManage and schedule cont</t>
+          <t>Geotrackers,&amp;nbsp;is hiring self motivated, result oriented professionals, with a flair for technology and loads of self-confidence, for the role of&amp;nbsp;Corporate Sales Manager/BDM.Job descriptionKRAs :Own, manage and drive sales in the Corporate &amp;amp; B2B segment in the stateCustomer consultatio</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>International Customer Sales &amp; Support</t>
+          <t>Business Operations Executive (Webinars &amp; Programs)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal</t>
+          <t>Mumbai Suburban, Maharashtra</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1169,26 +1165,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15000.0 - 25000.0</t>
+          <t>200000.0 - 400000.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>15000</v>
+        <v>200000</v>
       </c>
       <c r="M10" t="n">
-        <v>25000</v>
+        <v>400000</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24T18:25:40.232494Z</t>
+          <t>2026-06-05T18:25:06.122738Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2928575</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943188</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1198,24 +1194,24 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>We are looking for a talented International Customer Sales &amp;amp; Support Executive to join our growing telecommunications team. You’ll be the bridge between SMS Consortium and its international partners — ensuring smooth operations, professional communication, and reliable service delivery, while bu</t>
+          <t>About Wellness VibeWellness Vibe is a holistic wellness organization dedicated to emotional, mental, and overall well-being. We blend ancient yogic wisdom, sound-based practices, and modern facilitation tools to help individuals achieve clarity, balance, and conscious growth. Our programs include we</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Immigration Consultant</t>
+          <t>TRAINEE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>Star Trading Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>Palayamkottai, Tamil Nadu</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -1243,26 +1239,26 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20000.0 - 25000.0</t>
+          <t>180000.0 - 250000.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>20000</v>
+        <v>180000</v>
       </c>
       <c r="M11" t="n">
-        <v>25000</v>
+        <v>250000</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24T18:25:40.212497Z</t>
+          <t>2026-06-05T15:33:32.289708Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2928574</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2942589</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1272,32 +1268,28 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>• Engage in telephonic conversations with prospects and suggest the best immigration/visa options for Canada, Australia (PR Visa), Germany Opportunity Card, Portugal, Sweden, and other European countries.• Oversee all aspects of the Visa and Immigration Services process to ensure smooth and efficien</t>
+          <t>GENERAL, DAY TO DAY OPERATIONS WHICH INCLUDES COMMUNICATION, PACKING, BILLING, DISPATCH, ACCOUNTING AND STOCKING</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zed Facilitators</t>
+          <t>Recruitment of project staffs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Thane, Maharashtra</t>
-        </is>
-      </c>
+          <t>CSIR-CIMFR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="b">
         <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1315,28 +1307,20 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>22500.0 - 35500.0</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>22500</v>
-      </c>
-      <c r="M12" t="n">
-        <v>35500</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24T18:25:40.157474Z</t>
+          <t>2026-06-05T20:30:07.30681Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2928572</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2943357</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1346,28 +1330,28 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>We Are Hiring: ZED FacilitatorWe are looking for a dynamic, knowledgeable, and result-oriented ZED Facilitator to join our team. The ideal candidate will be responsible for guiding, training, and handholding MSMEs through the process of obtaining the ZED (Zero Defect Zero Effect) Certification to en</t>
+          <t>The selected Project Staff shall be engaged purely on a temporary basis for research and development activities related to the assigned project(s) in the areas of mining, fuel, energy, environmental management, allied engineering, and scientific disciplines. The incumbent will be responsible for car</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Cloud Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>SKODA AUTO VOLKSWAGEN INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1391,26 +1375,26 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100000.0 - 150000.0</t>
+          <t>1000000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="M13" t="n">
-        <v>150000</v>
+        <v>1500000</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-23T18:25:06.969873Z</t>
+          <t>2026-06-05T05:58:31.257457Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2926920</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2942287</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1420,28 +1404,28 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>We are looking for a highly skilled Senior Data Cloud Engineer. This is a remote-first opportunity for professionals who thrive at the intersection of Salesforce Data Cloud, AI, and enterprise data engineering.Role Details:- Experience: 8+ Years- CTC : As per Market&amp;nbsp;- Work Location: 100% Remote</t>
+          <t>Seeking a Mobile App Developer to design, build, and maintain mobile applications, ensuring functionality and user satisfaction. Responsibilities include developing app features, troubleshooting issues, and collaborating with cross-functional teams to meet project goals. Requirements: 5+ years' expe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Documents form fill Data entry work from home csc work</t>
+          <t>Picker Packer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VISHAL PRADIP SATTE</t>
+          <t>Essay Staffing Pvt Ltd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1475,12 +1459,12 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-23T00:50:15.815302Z</t>
+          <t>2026-06-05T04:02:04.587692Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2926611</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2942229</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1490,19 +1474,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>This is a form filling job from CSC which you can do from your mobile or laptop for which you will also be given training. To do this, only TEC certificate is required. If the candidate does not have it, then the hiring manager will guide you. This is work from home, part time. You have to work only</t>
+          <t>Seeking a Picker Packer to support warehouse operations, ensuring accurate order picking, packing, and timely dispatch. Responsibilities include picking items per order, scanning barcodes, maintaining speed and accuracy, and assisting in inventory management. Requirements: 0-2 years of experience in</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Catalog Analyst</t>
+          <t>Billing and cashier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>Jamnadas and co</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1535,26 +1519,26 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>180000.0 - 300000.0</t>
+          <t>150000.0 - 200000.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>180000</v>
+        <v>150000</v>
       </c>
       <c r="M15" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-22T18:25:06.144892Z</t>
+          <t>2026-06-05T02:45:41.173362Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2925691</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2942217</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1564,19 +1548,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Hi,We have opening for freshers &amp;amp; experienced for Catalog Analyst.Responsibilities:- Upload and manage product listings on various e-commerce platforms.- Ensure accurate and up-to-date product information, including specifications, images, and pricing.- Collaborate with cross-functional teams to</t>
+          <t>Looking for female candidates for counter system billing work. Candidates with knowledge in computer are preferred.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BD Executive</t>
+          <t>Counter sales girl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>Jamnadas and co</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1609,26 +1593,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200000.0 - 360000.0</t>
+          <t>120000.0 - 200000.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M16" t="n">
         <v>200000</v>
-      </c>
-      <c r="M16" t="n">
-        <v>360000</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-22T15:17:35.857847Z</t>
+          <t>2026-06-05T02:41:54.193319Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2925499</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2942216</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1638,24 +1622,24 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1. Identifying opportunities for new business development through following up leads on conducting research on target clients2. Managing the sales process to close new business opportunities3.building strong relationships with the existing portfolio of clients4. collaborating with management on sale</t>
+          <t>Looking for counter sales girls to attend customers. Candidates with knowledge in mobile what's app are preferred.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Backend associate</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>Jamnadas and co</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -1683,26 +1667,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15000.0 - 45000.0</t>
+          <t>150000.0 - 250000.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M17" t="n">
-        <v>45000</v>
+        <v>250000</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-22T15:17:35.836151Z</t>
+          <t>2026-06-05T02:32:27.50818Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2925498</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2942214</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1712,14 +1696,14 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>We are looking for a Backend Sales Executive who can support the sales team by managing customer data, preparing quotations, processing orders, and coordinating with clients and internal departments. The candidate should have good communication and computer skills.</t>
+          <t>Looking for a admin and admin asst. Candidates with previous experience and freshers can apply. Female candidates are preferred.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bank KYC Executive / KYC Analyst</t>
+          <t>Sales team leader</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1727,7 +1711,11 @@
           <t>Vee technologies pvt ltd</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gandhinagar, Gujarat</t>
+        </is>
+      </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
@@ -1753,26 +1741,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15000.0 - 22000.0</t>
+          <t>30000.0 - 60000.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="M18" t="n">
-        <v>22000</v>
+        <v>60000</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-22T15:17:35.788771Z</t>
+          <t>2026-06-04T18:25:07.084783Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2925496</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2941817</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1782,14 +1770,14 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Job SummaryThe KYC Executive is responsible for verifying customer identity, reviewing account opening documents, and ensuring compliance with banking regulations and Anti-Money Laundering (AML) policies. The role helps prevent fraud, financial crime, and unauthorized transactions.Key Responsibiliti</t>
+          <t>Sales Team Leader:Exp: 3 to 6 years in any manufacturing industry ( Electrical background will be preferred)Education: Any degree ( B.tech in electrical or technical background will be preferred.)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Trainees as Company Secretary ICSI and Semi-Qualified CS</t>
+          <t>PLACEMENT HEAD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1799,7 +1787,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Delhi, New Delhi, Uttar Pradesh</t>
+          <t>Kozhikode, Kerala</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -1827,26 +1815,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7000.0 - 30000.0</t>
+          <t>40000.0 - 70000.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="M19" t="n">
-        <v>30000</v>
+        <v>70000</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-21T18:25:06.811923Z</t>
+          <t>2026-06-04T18:25:07.061761Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2923872</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2941816</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1856,14 +1844,14 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>We are looking for 3 Trainees for the Company Secretary 21 Months and 2 Semi-Qualified Company Secretaries.Location: Noida (Sector 63 &amp;amp; 2), UP and Delhi (Netaji Subhash Place) Department: Legal &amp;amp; ComplianceEmployment Type: Full-timeQualifications:For Semi-Qualified CS: Completed CS Professio</t>
+          <t>We are looking for a dynamic and result-oriented Placement Coordinator Head to lead our placement and corporate relations activities. The ideal candidate will be responsible for establishing and maintaining strong industry connections, building and managing a placement team, and ensuring successful</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Talent Acquisition Specialist</t>
+          <t>Business Development Executive</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1873,7 +1861,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vadodara, Gujarat</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -1901,26 +1889,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18000.0 - 20000.0</t>
+          <t>250000.0 - 600000.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>18000</v>
+        <v>250000</v>
       </c>
       <c r="M20" t="n">
-        <v>20000</v>
+        <v>600000</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-21T18:25:06.784672Z</t>
+          <t>2026-06-04T18:25:07.040407Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2923871</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2941815</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1930,14 +1918,14 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Job Title: Talent Acquisition SpecialistLocation: Vadodara, GujaratEmployment Type: Full-time, PermanentImportant Note: This is a night shift role (7:00 PM – 5:00 AM IST).Freshers and recent graduates are encouraged to apply!Role Overview:We’re looking for a dynamic Talent Acquisition Specialist to</t>
+          <t>Job OverviewWe are looking for an enthusiastic and driven Business Development Executive (BDE) to join our wedding photography team. This role is ideal who are passionate about sales, client interaction, and the wedding industry. The role involves handling inquiries, coordinating with potential clie</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Coordinator</t>
+          <t>Talent Acquisition Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1947,7 +1935,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Muzaffarpur, Bihar</t>
+          <t>Vadodara, Gujarat</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -1975,26 +1963,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12000.0 - 18000.0</t>
+          <t>18000.0 - 20000.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="M21" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-21T18:25:06.706169Z</t>
+          <t>2026-06-04T18:25:07.003813Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2923868</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2941814</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2004,32 +1992,32 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>🚨 Hiring: System Coordinator📍 Location: Muzaffarpur, Bihar🏢 Company: Sri Dhanganga Marble &amp;amp; Tiles(Authorized Kajaria Ceramics Distributor since 1993)We are looking for a responsible and organized System Coordinator to support showroom operations and customer coordination.✨ Key Responsibilities:•</t>
+          <t>Title: Talent Acquisition Specialist (Fresher)Location: Atladra, Vadodara, Gujarat (On-Site)Timings: 7:00 PM IST – 5:00 AM IST (Night Shift)Main Responsibilities of Talent Acquisition Specialist (Fresher):MUST HAVE GOOD COMMAND OVER SPOKEN, LISTENING AND WRITTEN ENGLISH LANGUAGE.1. Review the job de</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Computer Operator</t>
+          <t>Junior Research Associate / Research Trainee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shivanshu Cafe</t>
+          <t>ITC Life Sciences And Technology Centre</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gaya, Bihar</t>
+          <t>Bengaluru, Karnataka</t>
         </is>
       </c>
       <c r="D22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2049,26 +2037,26 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5000.0 - 10000.0</t>
+          <t>180000.0 - 450000.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>5000</v>
+        <v>180000</v>
       </c>
       <c r="M22" t="n">
-        <v>10000</v>
+        <v>450000</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-21T09:18:06.984993Z</t>
+          <t>2026-06-04T09:59:06.686866Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2923476</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2940999</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2078,14 +2066,14 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Work from home. a to z cyber cafe related work karna hai. agar koi problem aati hai to aapko remotely help kiya jayega..</t>
+          <t>Responsibilities : Supporting team with data collection, lab experiments and quality analysis of products. Assisting in project management tasks like documentation, Quality analysis &amp; literature search. ' Fresher with good Academic background &amp; good communication skills . Education : M.Sc in any Sci</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Social media marketing</t>
+          <t>HR Recruiter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2095,7 +2083,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -2123,26 +2111,26 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15000.0 - 40000.0</t>
+          <t>20000.0 - 25000.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="M23" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-20T18:25:06.344443Z</t>
+          <t>2026-06-03T18:25:06.223266Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2921251</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2940238</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2152,14 +2140,14 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>About Purple United KidsPurple United Kids is a premium fashion brand dedicated to creating stylish, high-quality apparel and footwear for children. With a focus on comfort, durability, and design, we blend playful creativity with modern trends to empower young personalities to shine. Our collection</t>
+          <t>Job Title&amp;nbsp;: HR RecruiterLocation : Naigaon, Mumbai (On-site)Job Type : Full-timeWorking Hours : 9:00 AM – 6:00 PMTransportation : Company pick-up and drop facility available from the highway.Job Responsibilities Source candidates through job portals and social media platforms.Screen resumes and</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Business Development Manager &amp; Lead Generation Executive</t>
+          <t>Senior Associate – Admin &amp; HR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2169,7 +2157,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -2197,26 +2185,26 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20000.0 - 25000.0</t>
+          <t>60000.0 - 70000.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="M24" t="n">
-        <v>25000</v>
+        <v>70000</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-20T18:25:06.3259Z</t>
+          <t>2026-06-03T18:25:06.186935Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2921250</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2940237</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2226,14 +2214,14 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Dexcom Enterprises is seeking a dynamic and result-oriented Business Development &amp;amp; Lead Generation Executive to drive business growth, build strategic client relationships, and generate qualified leads across domestic and international markets.The role demands a proactive professional who can id</t>
+          <t>Purpose of the Role: To support the management by streamlining key HR, administration, compliance, and operational processes across the organisation.Role &amp; Responsibilities:Manage the end-to-end employee life cycle for employees, interns, consultants, and contracted team members, including recruitme</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Academic Counsellors</t>
+          <t>Correspondent</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2243,7 +2231,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kozhikode, Kerala</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -2271,13 +2259,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>23000.0 - 30000.0</t>
+          <t>18000.0 - 30000.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>23000</v>
+        <v>18000</v>
       </c>
       <c r="M25" t="n">
         <v>30000</v>
@@ -2285,12 +2273,12 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-20T18:25:06.304069Z</t>
+          <t>2026-06-02T18:25:06.611699Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2921249</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2939063</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2300,32 +2288,28 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Job description:Senior Academic Counsellor – Job DescriptionLocation: KozhikodeExperience: 3–5 YearsIndustry Preference: EdTechAbout the RoleWe are looking for a dynamic and result-oriented Senior Academic Counsellor to join our team. Theideal candidate should have prior experience in the EdTech ind</t>
+          <t>Who We’re Looking ForWe are looking for a sharp and passionate Journalist from the content writing / media industry who can turn industry updates into compelling stories. If you have a strong news sense, excellent writing skills, and the confidence to engage with senior aviation professionals, this</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Academic Counsellors</t>
+          <t>Data Entry work from home csc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Kozhikode, Kerala</t>
-        </is>
-      </c>
+          <t>GOOGLE INDIA PRIVATE LIMTED</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="b">
         <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2345,26 +2329,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23000.0 - 30000.0</t>
+          <t>25000.0 - 3000000.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="M26" t="n">
-        <v>30000</v>
+        <v>3000000</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-20T18:25:06.274153Z</t>
+          <t>2026-06-02T08:27:34.729756Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2921248</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2938589</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2374,24 +2358,24 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Job description:Senior Academic Counsellor – Job DescriptionLocation: KozhikodeExperience: 3–5 YearsIndustry Preference: EdTechAbout the RoleWe are looking for a dynamic and result-oriented Senior Academic Counsellor to join our team. Theideal candidate should have prior experience in the EdTech ind</t>
+          <t>This is data entry form fillings work Training also provided After training joining letter provide This is under csc work so all work Done through csc portal Tec certificate required if candidates don't have tec certificate no we are helping to get this certificate We are not connect through mail.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Medical equipments and Instruments</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SHANTI SENIOR CITIZEN SERVICES PRIVATE LIMITED</t>
+          <t>Vee technologies pvt ltd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Himatnagar, Gujarat</t>
+          <t>Chengalpattu, Tamil Nadu, Chennai</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -2399,7 +2383,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2419,26 +2403,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>30000.0 - 1000000.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="M27" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-20T11:32:42.552273Z</t>
+          <t>2026-06-01T18:25:13.939869Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2920860</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2937912</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2448,22 +2432,26 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Promote and sell medical equipment to hospitals and clinics Generate leads and follow up with customers Conduct product presentations and demonstrations Support digital marketing and social media activities Maintain client relationships and achieve sales targets Skills Required Good communication an</t>
+          <t>About VanbreyVanbrey is a premier management and strategy consulting firm dedicated to delivering transformative solutions to clients across industries. We partner with organizations to drive performance, accelerate growth, and navigate complex business challenges. As we continue to scale our client</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>MESS MANAGER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CSIR-CIMFR</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>PARTHA SARATHI SERVICES (OPC) PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LINGARAJ, Odisha</t>
+        </is>
+      </c>
       <c r="D28" t="b">
         <v>0</v>
       </c>
@@ -2489,26 +2477,26 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19900.0 - 37000.0</t>
+          <t>180000.0 - 240000.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>19900</v>
+        <v>180000</v>
       </c>
       <c r="M28" t="n">
-        <v>37000</v>
+        <v>240000</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-05-19T20:30:25.680102Z</t>
+          <t>2026-05-29T13:39:24.688568Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2918955</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2935543</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2518,22 +2506,26 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Responsible for providing technical support in laboratories, workshops, pilot plants, and research projects. The role involves operation, maintenance, testing, calibration, installation, and repair of scientific instruments, machines, and equipment used in research and development activities. Techni</t>
+          <t>Seeking a Mess Manager to oversee canteen operations, ensure hygiene standards, and manage staff efficiently. Responsibilities include supervising daily food service, maintaining cleanliness, and coordinating staff schedules. Requirements: 5+ years of experience in food service or hospitality, stron</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mechanical engineer</t>
+          <t>Fundraising Officer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IWTRS PVT LTD</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
       <c r="D29" t="b">
         <v>0</v>
       </c>
@@ -2559,26 +2551,26 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>240000.0 - 300000.0</t>
+          <t>21000.0 - 40000.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>240000</v>
+        <v>21000</v>
       </c>
       <c r="M29" t="n">
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-05-19T11:45:09.42416Z</t>
+          <t>2026-05-28T18:25:07.0275Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2918376</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2934268</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2588,14 +2580,14 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Handle mechanical O&amp;M of ZLD/ETP plant equipment. Ensure 24x7 uptime of pumps, blowers, centrifuges, MEE, ATFD, UF/RO skids. Reduce breakdowns &amp; improve efficiency.Plant O&amp;M: Daily monitoring of pumps, gearboxes, blowers, agitators, screw press, centrifuge, MEE, ATFD, RO skids, valves, pipelinesPrev</t>
+          <t>🌱 We’re Hiring | Fundraising Officer – WWF-India (Delhi Office) 🐼Are you passionate about communication, networking, and creating meaningful impact? Join WWF-India, one of the world’s leading conservation organizations, and contribute towards protecting wildlife and nature.Position: Fundraising Offi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Digital and Social Media Executive</t>
+          <t>Graphic designer and Video Editor</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2605,7 +2597,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bareilly, Uttar Pradesh</t>
+          <t>Panchkula, Haryana</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -2633,26 +2625,26 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12000.0 - 22000.0</t>
+          <t>15000.0 - 20000.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="M30" t="n">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-05-18T18:25:06.20301Z</t>
+          <t>2026-05-28T18:25:07.007223Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2916227</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2934267</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2662,14 +2654,14 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>📢 We’re Hiring | Social Media Executive🏫 Industry: Advertising📍 Location: Bareilly🧑‍💼 Experience: Minimum 2 Years💰 Salary: Up to ₹20,000👩 Eligibility: Only Female Candidates🔑 Key Skills:✔️ Social Media Management (Instagram, Facebook, LinkedIn)✔️ Content Creation &amp;amp; Creative Writing✔️ Reels &amp;amp;</t>
+          <t>TYPE OF JOB : FREELANCER / PART-TIME / FULL TIME / STUDENT JOBREQUIREMENTS:Required Young Creative Person with Proficiency in video editing software such as Adobe Premier pro, After Effects, DaVinci ResolveStrong understanding of cinematic editing, transitions, sound design and color gradingKnowledg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Customer Support Executive</t>
+          <t>Junior Store Executive</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2679,7 +2671,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Delhi, New Delhi, Uttar Pradesh</t>
+          <t>Palghar, Maharashtra</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -2707,26 +2699,26 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16000.0 - 20000.0</t>
+          <t>20000.0 - 25000.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="M31" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-05-18T18:25:06.166363Z</t>
+          <t>2026-05-28T18:25:06.989863Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2916225</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2934266</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2736,26 +2728,22 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Urgently hiring for Customer Support ExecutiveAny Graduate and Post Graduate can applyFreshers with strong communication and confidence are welcome to apply.Must own a LaptopStart Day: Immediate JoinersAbout the RoleWe are looking for a dynamic and enthusiastic Customer Support Executive to join our</t>
+          <t>Job Summary:Manage inward and outward of raw materials, packing materials, and finished&amp;nbsp;goods.Maintain accurate inventory records and stock levels. Ensure proper storage and handling of materials to avoid damage or loss. Follow FIFO (First In First Out) for material issuance and usage. Prepare</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Customer Support Executive</t>
+          <t>Senior Manager Mechanical</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Delhi, Uttar Pradesh, New Delhi</t>
-        </is>
-      </c>
+          <t>HPCL Rajasthan Refinery Limited</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="b">
         <v>0</v>
       </c>
@@ -2781,26 +2769,26 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16000.0 - 20000.0</t>
+          <t>2400000.0 - 2500000.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>16000</v>
+        <v>2400000</v>
       </c>
       <c r="M32" t="n">
-        <v>20000</v>
+        <v>2500000</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-05-18T18:25:06.132147Z</t>
+          <t>2026-05-28T10:23:42.006768Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2916224</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2933975</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2810,24 +2798,24 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Urgently hiring for Customer Support ExecutiveAny Graduate and Post Graduate can applyFreshers with strong communication and confidence are welcome to apply.Must own a LaptopStart Day: Immediate JoinersAbout the RoleWe are looking for a dynamic and enthusiastic Customer Support Executive to join our</t>
+          <t>Visit hrrl.in Coordinate with Internal &amp; External Stakeholders for job execution including Pre commissioning/commissioning, startup and test runs. Accountable to ensure continuous running of the Refinery &amp; Petrochemical Plants to meet the production targets. • Lead the team implementation of predict</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>graphics designer cum digital marketing</t>
+          <t>required accountant with adequate knowledge in tally excel and word</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mindpik Technologies Private Limited</t>
+          <t>NISITH ROY &amp; CO.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal, Bidhannagar</t>
+          <t>Kolkata, West Bengal</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -2855,26 +2843,26 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10000.0 - 120000.0</t>
+          <t>15000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="M33" t="n">
-        <v>120000</v>
+        <v>1500000</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-05-18T12:50:02.30652Z</t>
+          <t>2026-05-28T04:39:28.166672Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2915772</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2933843</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2884,24 +2872,24 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Key Roles &amp; Responsibilities Creative &amp; Graphic Design (50%) Marketing Collateral: Design visually compelling assets including social media posts/carousels, display ads, Google Performance Max creatives, website banners, landing page layouts, and email templates. Brand Identity: Ensure strict adhere</t>
+          <t>Seeking an Accountant to support financial operations with proficiency in Tally, Excel, and Word. Entry-level role for 0-2 years’ experience. Responsibilities include maintaining financial records, preparing reports, and ensuring data accuracy. Requirements: Strong knowledge of Tally, Excel, Word, a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Warehouse Executive</t>
+          <t>GNM Staff Nurse</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AASAANJOBS PRIVATE LIMITED</t>
+          <t>Vee technologies pvt ltd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>achhanpur b.o, HARYANA</t>
+          <t>Mumbai, Maharashtra, Mumbai Suburban</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -2927,20 +2915,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15000.0 - 35000.0</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>35000</v>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-05-18T20:30:29.926572Z</t>
+          <t>2026-05-27T18:25:06.245156Z</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2916974</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2932781</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2950,22 +2946,26 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Picking products from warehouse racks as per order requirements. Packing items safely and accurately for dispatch. Loading and unloading goods from vehicles and containers. Sorting, scanning, labeling, and organizing inventory. Maintaining cleanliness and safety standards in the warehouse. Ensuring</t>
+          <t>We are hiring Staff Nurses for Hospital based in MumbaiQualification : ANM/GNM/BSC - NursingExperience : 0 to 4 yearsCandidates should have Maharashtra Nursing Council registrationSalary : Based on experienceFree food and accomodation provided for female candidates</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Warehouse Associate</t>
+          <t>BUSINESS SALES EXECUTIVE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AASAANJOBS PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Karnataka, Chennai, Tamil Nadu, Hyderabad, Telangana</t>
+        </is>
+      </c>
       <c r="D35" t="b">
         <v>0</v>
       </c>
@@ -2991,26 +2991,26 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15000.0 - 18000.0</t>
+          <t>25000.0 - 35000.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="M35" t="n">
-        <v>18000</v>
+        <v>35000</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-05-18T20:30:32.416775Z</t>
+          <t>2026-05-27T18:25:06.201831Z</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2917132</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2932779</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3020,26 +3020,22 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Logistics Executive is responsible for managing dispatch, transportation, inventory tracking, and delivery coordination. Ensures timely shipment, vendor coordination, documentation, and smooth supply chain operations</t>
+          <t>Job Title: Sales Demo Team MemberWork Mode: On-Field/ Full-TimeAbout UsVatech India Pvt. Ltd. is a pioneer in dental imaging solutions, offering digital X-ray and 3D imaging systems along with diagnostic software. Based in New Delhi, the company combines global expertise with strong local support to</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Virtual Relationship Manager</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana</t>
-        </is>
-      </c>
+          <t>SAIRA PEOPLE TECH SOLUTIONS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="b">
         <v>0</v>
       </c>
@@ -3063,28 +3059,20 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12000.0 - 15000.0</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>12000</v>
-      </c>
-      <c r="M36" t="n">
-        <v>15000</v>
-      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-05-17T18:25:42.377003Z</t>
+          <t>2026-05-27T20:30:29.830224Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2914689</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2933363</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3094,32 +3082,28 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Inside Sales Intern – Seoak InnovationsLocation: Madhapur, HyderabadDuration: 3 MonthsStipend: ₹15,000/monthRole:Talk to potential customers (calls/messages)Explain services and generate leadsFollow up and help convert leadsRequirements:Good communication skillsImmediate joiners preferredFreshers ca</t>
+          <t>Customer engagement through phone/chat/email, CRM handling, portfolio support, and digital banking assistance.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Development Manager</t>
+          <t>HR EXECUTIVE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Mumbai, Maharashtra</t>
-        </is>
-      </c>
+          <t>Essay Staffing Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="b">
         <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3139,26 +3123,26 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20000.0 - 50000.0</t>
+          <t>10000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="M37" t="n">
-        <v>50000</v>
+        <v>1500000</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-05-16T18:25:08.185879Z</t>
+          <t>2026-05-27T07:06:36.839485Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2913809</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2932343</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3168,14 +3152,14 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Connect on : 8454836438 or pcred.rambo@gmail.comJob Description: Business Development ManagerTimings :10am to 7pm (only Sunday off)Salary: depends on the experience1.Develop and implement strategic sales plans to achieve company objectives and revenue targets.2.Identify and pursue new business oppor</t>
+          <t>job Overview Hum ek energetic aur result-oriented HR Recruiter ki talash mein hain jo hamari company ke liye sahi talent ko dhoodhne, attract karne aur hire karne mein madad kare. Aapka main kaam talent sourcing se lekar onboarding tak ke process ko smoothly manage karna hoga. Agar aapke paas achhi</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>House Keeping</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3185,7 +3169,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Mumbai, Maharashtra, Mumbai Suburban</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -3213,26 +3197,26 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25000.0 - 40000.0</t>
+          <t>14000.0 - 21000.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>25000</v>
+        <v>14000</v>
       </c>
       <c r="M38" t="n">
-        <v>40000</v>
+        <v>21000</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-05-16T18:25:08.146525Z</t>
+          <t>2026-05-26T18:25:13.136045Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2913807</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2931255</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3242,32 +3226,28 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Walls Asia Architects &amp;amp; Engineers is hiring an Architect with 2-3 years of experience for residential and commercial projects in Hyderabad.Roles &amp;amp; Responsibilities:• Prepare architectural concepts and detailed drawings• Work on residential and commercial projects• Coordinate with clients, en</t>
+          <t>Job Title: Office Boy/ Office Assistant&amp;nbsp;We are looking for hardworking and reliable individuals to assist in the daily operations of our Borivali office. This is a great opportunity for candidates with SSC qualification looking for a stable environment.Key Responsibilities: • Office Maintenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Instructional Design - Associate Manager</t>
+          <t>Civil Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bengaluru Urban, Karnataka</t>
-        </is>
-      </c>
+          <t>RITES LIMITED</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="b">
         <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3287,26 +3267,26 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2000000.0 - 2244000.0</t>
+          <t>30000.0 - 160000.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>2000000</v>
+        <v>30000</v>
       </c>
       <c r="M39" t="n">
-        <v>2244000</v>
+        <v>160000</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-05-16T18:25:08.126335Z</t>
+          <t>2026-05-26T20:30:27.094119Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2913806</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2931726</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3316,14 +3296,14 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Learning Experience Design &amp;amp; Development – Associate Manager (CL8)We are hiring for the role of Instructional Design – Associate Manager (CL8) for a dynamic and global team environment.Job Details:Role: Learning Experience Design &amp;amp; Development – Associate ManagerLocation: BengaluruCTC: As pe</t>
+          <t>1. Minimum 10 years of experience in execution/supervision of STP, WTP, Drainage, MPS, WSS, Sewage Treatment Plants, Water Supply Systems, Infrastructure, and Building Works. 2. Minimum 5 years of experience in execution/supervision of STP, WTP, Drainage, WSS, Sewage Treatment Plants, Water Supply S</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>German Language Expert (HR Operations)</t>
+          <t>collection executive</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3333,7 +3313,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bengaluru Urban, Karnataka</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -3361,26 +3341,26 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>400000.0 - 800000.0</t>
+          <t>240000.0 - 300000.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>400000</v>
+        <v>240000</v>
       </c>
       <c r="M40" t="n">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-05-16T18:25:08.084884Z</t>
+          <t>2026-05-25T18:25:07.033359Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2913805</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2929586</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3390,24 +3370,24 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Job Title: HR Operations Associates Shift Timings: 1 PM to 11 PM IST.CTC :- As per market&amp;nbsp;Location:- Bengalore Must have skill: Proficient in German Speaking and Writing (B1 / C1+)Good to have skill: HRO Skill Hire to Retire, MS office Shift Timings: 1 PM to 11 PM IST. Should be comfortable wit</t>
+          <t>🎯 Role OverviewThe Collection Associate is responsible for managing outstanding customer accounts, ensuring timely collection of payments, and maintaining positive client relationships. This role plays a key part in safeguarding the company’s cash flow and minimizing bad debt.📋 Key ResponsibilitiesC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Executive - Recruitments</t>
+          <t>Content Writer Intern</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kapgrow Corporate Advisory Services Pvt Ltd</t>
+          <t>Vee technologies pvt ltd</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -3435,26 +3415,26 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12000.0 - 30000.0</t>
+          <t>9000.0 - 10000.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="M41" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-05-16T11:37:31.718883Z</t>
+          <t>2026-05-25T18:25:06.988939Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2913516</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2929584</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3464,14 +3444,14 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Seeking an Executive - Recruitments to manage end-to-end hiring processes for consultancy clients, ensuring top talent acquisition. Responsibilities include sourcing, screening, scheduling interviews, and coordinating with clients to fulfill recruitment needs efficiently. Requirements: Bachelor’s de</t>
+          <t>Job Description: You will assist our content and marketing team in creating high-quality, engaging, and SEO-friendly content for managed websites&amp;nbsp;and digital platforms. The role involves researching topics, writing and editing content, and optimizing published articles to improve&amp;nbsp;readabili</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>"Inside sales Representative required @Gurgaon</t>
+          <t>Web Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3481,7 +3461,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Karnataka, Haryana, Pune, Maharashtra</t>
+          <t>Kolkata, West Bengal</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -3509,26 +3489,26 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>250000.0 - 350000.0</t>
+          <t>15000.0 - 40000.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>250000</v>
+        <v>15000</v>
       </c>
       <c r="M42" t="n">
-        <v>350000</v>
+        <v>40000</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-05-14T14:31:11.021104Z</t>
+          <t>2026-05-25T18:25:06.946647Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2909606</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2929583</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3538,24 +3518,24 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>- Job Description:&amp;nbsp; &amp;nbsp; - Drive walk-ins from inbound leads&amp;nbsp; &amp;nbsp; - Pre-qualify, counsel, and convert leads&amp;nbsp; &amp;nbsp; - Call inbound leads using LeadSquared CRM&amp;nbsp; &amp;nbsp; - Counsel prospects on Emversity programmes&amp;nbsp; &amp;nbsp; - Book and drive physical walk-in demos- Requiremen</t>
+          <t>Job Description:Liberating Solution Pvt. Ltd. is looking for a motivated Web Consultant with experience in outbound calling and client communication. The candidate will be responsible for connecting with potential clients, understanding their digital requirements, and closing deals for website and d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Customer Support Executive</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
+          <t>AAM Foundation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Chitrakoot Dham, Uttar Pradesh</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -3583,26 +3563,26 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16000.0 - 20000.0</t>
+          <t>174000.0 - 194000.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>16000</v>
+        <v>174000</v>
       </c>
       <c r="M43" t="n">
-        <v>20000</v>
+        <v>194000</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-05-14T14:30:17.177719Z</t>
+          <t>2026-05-25T09:36:13.340673Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2909605</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2929219</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3612,14 +3592,14 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Easy Settlement, is a leading provider of financial and legal services specializing in loan settlement and debt resolution. Our mission is to assist individuals and businesses burdened by personal loans, credit card debts, and EMI challenges by offering customized solutions.With a dedicated team of</t>
+          <t>Job Responsibilities • Travel to and teach at local villages. • Mobilize (find) new students in areas near the branch so that the branch has 70+ students. • Conduct 4 classes of 1 hour 40 mins daily, each with 18-20 students. • Handle 30 minutes of admin work daily. • Ensure full engagement with FEA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Digital and Social Media Executive</t>
+          <t>Zed Facilitators</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3629,7 +3609,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Thane, Maharashtra</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -3657,26 +3637,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10000.0 - 30000.0</t>
+          <t>22500.0 - 35500.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>10000</v>
+        <v>22500</v>
       </c>
       <c r="M44" t="n">
-        <v>30000</v>
+        <v>35500</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-05-14T13:48:53.46389Z</t>
+          <t>2026-05-24T18:25:40.157474Z</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2909602</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2928572</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3686,32 +3666,28 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Job Title: Social Media Executive**Location: Mumbai**Experience:** 1+ Years**Industry:** PR Agency### Job DescriptionWe are looking for a creative and proactive Social Media Executive to join our team in Mumbai. The ideal candidate should have hands-on experience in managing social media platforms,</t>
+          <t>We Are Hiring: ZED FacilitatorWe are looking for a dynamic, knowledgeable, and result-oriented ZED Facilitator to join our team. The ideal candidate will be responsible for guiding, training, and handholding MSMEs through the process of obtaining the ZED (Zero Defect Zero Effect) Certification to en</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>customer service executive</t>
+          <t>Documents form fill Data entry work from home csc work</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vee technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
+          <t>VISHAL PRADIP SATTE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3731,26 +3707,26 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>240000.0 - 300000.0</t>
+          <t>15000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>240000</v>
+        <v>15000</v>
       </c>
       <c r="M45" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-05-14T13:48:53.424425Z</t>
+          <t>2026-05-23T00:50:15.815302Z</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2909601</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2926611</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3760,14 +3736,14 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Customer Support Executive (Voice &amp;amp; Email Process) – English, Hindi &amp;amp; Any Native LanguageWe’re looking for candidates with 1–2 years of experience in customer support, preferably in voice Bpo, who are strong in customer service skills and delivering great customer experiences.🔧 Responsibilit</t>
+          <t>This is a form filling job from CSC which you can do from your mobile or laptop for which you will also be given training. To do this, only TEC certificate is required. If the candidate does not have it, then the hiring manager will guide you. This is work from home, part time. You have to work only</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Customer Support Executive</t>
+          <t>Catalog Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3777,7 +3753,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -3805,26 +3781,26 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15000.0 - 20000.0</t>
+          <t>180000.0 - 300000.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>15000</v>
+        <v>180000</v>
       </c>
       <c r="M46" t="n">
-        <v>20000</v>
+        <v>300000</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-05-14T13:37:48.678673Z</t>
+          <t>2026-05-22T18:25:06.144892Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2909599</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2925691</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3834,14 +3810,14 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>We’re Hiring: Customer Support Executive – International (Voice &amp;amp; Chat)Location: KolkataShifts: Rotational (Day/Night)Experience: 1–3 YearsDepartment: Customer Support / Operations________________________________________Job Summary:We are looking for dynamic professionals to join our Internation</t>
+          <t>Hi,We have opening for freshers &amp;amp; experienced for Catalog Analyst.Responsibilities:- Upload and manage product listings on various e-commerce platforms.- Ensure accurate and up-to-date product information, including specifications, images, and pricing.- Collaborate with cross-functional teams to</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Customer Success Consultant</t>
+          <t>BD Executive</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3851,7 +3827,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -3879,26 +3855,26 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>300000.0 - 500000.0</t>
+          <t>200000.0 - 360000.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="M47" t="n">
-        <v>500000</v>
+        <v>360000</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-05-14T13:37:48.636747Z</t>
+          <t>2026-05-22T15:17:35.857847Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2909598</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2925499</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3908,22 +3884,26 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Location : Bangalore, Mumbai, Ahmedabad🕐 Notice Period : Immediate Joiners Preferred👤 Role : Customer Success Consultant ( Freshers can also apply)🎓 Education : Any Graduate / Post Graduate🛠️ Skills We’re Looking For:- Business Development- Lead Generation through Channel partners- Customer Success-</t>
+          <t>1. Identifying opportunities for new business development through following up leads on conducting research on target clients2. Managing the sales process to close new business opportunities3.building strong relationships with the existing portfolio of clients4. collaborating with management on sale</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sales Administration and Commercial Officer</t>
+          <t>Trainees as Company Secretary ICSI and Semi-Qualified CS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Saira People Tech Solutions Private Limited</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Delhi, New Delhi, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="D48" t="b">
         <v>0</v>
       </c>
@@ -3949,26 +3929,26 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>400000.0 - 600000.0</t>
+          <t>7000.0 - 30000.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>400000</v>
+        <v>7000</v>
       </c>
       <c r="M48" t="n">
-        <v>600000</v>
+        <v>30000</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-05-13T12:11:40.495052Z</t>
+          <t>2026-05-21T18:25:06.811923Z</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2906366</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2923872</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3978,24 +3958,28 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Administrative support for Project Sales Team, Advanced MS Excel, SAP tool, Accounting and Taxation knowledge, Reporting skills, Vendor management, Commercial knowledge. Accurate dealer level sales reports as per requirement. Logistics and operational support to Unit level initiatives.Employee life</t>
+          <t>We are looking for 3 Trainees for the Company Secretary 21 Months and 2 Semi-Qualified Company Secretaries.Location: Noida (Sector 63 &amp;amp; 2), UP and Delhi (Netaji Subhash Place) Department: Legal &amp;amp; ComplianceEmployment Type: Full-timeQualifications:For Semi-Qualified CS: Completed CS Professio</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Project Technical Support-III</t>
+          <t>Computer Operator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>E-SOLUTIONS IT SERVICES PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Shivanshu Cafe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gaya, Bihar</t>
+        </is>
+      </c>
       <c r="D49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4019,26 +4003,26 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>5000.0 - 10000.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="M49" t="n">
-        <v>1500000</v>
+        <v>10000</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-05-13T04:54:40.415881Z</t>
+          <t>2026-05-21T09:18:06.984993Z</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2906121</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2923476</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4048,19 +4032,19 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Project entitled-: “Equitable, Quality universal health coverage Implementation research Project for optimizing comprehensive primary health care through Health and Wellness Centres in Primpri Chinchwad Municipal Corporation, Pune district of Maharashtra- EQUIP-HWCs” funded by Indian Council of Medi</t>
+          <t>Work from home. a to z cyber cafe related work karna hai. agar koi problem aati hai to aapko remotely help kiya jayega..</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUPER DISTRIBUTER</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PARTHA SARATHI SERVICES (OPC) PRIVATE LIMITED</t>
+          <t>CSIR-CIMFR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -4069,7 +4053,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4089,26 +4073,26 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>19900.0 - 37000.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>15000</v>
+        <v>19900</v>
       </c>
       <c r="M50" t="n">
-        <v>1500000</v>
+        <v>37000</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-05-08T10:01:45.831929Z</t>
+          <t>2026-05-19T20:30:25.680102Z</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2897498</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2918955</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4118,26 +4102,22 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Seeking a Super Distributor to drive monthly sales targets by managing and coordinating team efforts across master distributors and distributors. Responsibilities: Achieve monthly sales targets through effective team leadership. Monitor distributor performance and ensure alignment with goals. Report</t>
+          <t>Responsible for providing technical support in laboratories, workshops, pilot plants, and research projects. The role involves operation, maintenance, testing, calibration, installation, and repair of scientific instruments, machines, and equipment used in research and development activities. Techni</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business developement</t>
+          <t>Mechanical engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>nashik, MAHARASHTRA</t>
-        </is>
-      </c>
+          <t>IWTRS PVT LTD</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="b">
         <v>0</v>
       </c>
@@ -4161,20 +4141,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>240000.0 - 300000.0</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>240000</v>
+      </c>
+      <c r="M51" t="n">
+        <v>300000</v>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-05-06T20:30:35.342283Z</t>
+          <t>2026-05-19T11:45:09.42416Z</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2894026</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2918376</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4184,22 +4172,26 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>LIC is hiring for Insurance policy advisor across India become certified LIC advisor and earn good monthly income</t>
+          <t>Handle mechanical O&amp;M of ZLD/ETP plant equipment. Ensure 24x7 uptime of pumps, blowers, centrifuges, MEE, ATFD, UF/RO skids. Reduce breakdowns &amp; improve efficiency.Plant O&amp;M: Daily monitoring of pumps, gearboxes, blowers, agitators, screw press, centrifuge, MEE, ATFD, RO skids, valves, pipelinesPrev</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BANKING JOB</t>
+          <t>graphics designer cum digital marketing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>banking career solution latur,training and placeme</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Mindpik Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Kolkata, West Bengal, Bidhannagar</t>
+        </is>
+      </c>
       <c r="D52" t="b">
         <v>0</v>
       </c>
@@ -4225,26 +4217,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>21000.0 - 25000.0</t>
+          <t>10000.0 - 120000.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>21000</v>
+        <v>10000</v>
       </c>
       <c r="M52" t="n">
-        <v>25000</v>
+        <v>120000</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-05-06T08:30:10.279413Z</t>
+          <t>2026-05-18T12:50:02.30652Z</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2545046</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2915772</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4254,26 +4246,22 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Join this group:- https://chat.whatsapp.com/BlZcHvLh57v0EmygqAT4HF?mode=gi_t 🏦 BANKING CAREER OPPORTUNITY - MAHARASHTRA 🏦 We are hiring for Equitas Small Finance Bank and Kotak Mahindra Bank (NextGen Program). Join one of India's fastest-growing banking sectors! 📅 Online Interview Schedule Process:</t>
+          <t>Key Roles &amp; Responsibilities Creative &amp; Graphic Design (50%) Marketing Collateral: Design visually compelling assets including social media posts/carousels, display ads, Google Performance Max creatives, website banners, landing page layouts, and email templates. Brand Identity: Ensure strict adhere</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Assembly technician</t>
+          <t>Warehouse Associate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Caruna mobility</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ganapathichettikulam, Puducherry</t>
-        </is>
-      </c>
+          <t>AASAANJOBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="b">
         <v>0</v>
       </c>
@@ -4299,26 +4287,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>150000.0 - 240000.0</t>
+          <t>15000.0 - 18000.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>150000</v>
+        <v>15000</v>
       </c>
       <c r="M53" t="n">
-        <v>240000</v>
+        <v>18000</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-05-05T05:15:17.459479Z</t>
+          <t>2026-05-18T20:30:32.416775Z</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2889551</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2917132</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4328,22 +4316,26 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>We are looking for assembly specialists, who can also quality check the spare parts coming in from suppliers, for wheelchair fitting. Also automotive wire joining work. Check our products page on website to understand. Technician must also know how to solder. Other skills required include: 1. using</t>
+          <t>Logistics Executive is responsible for managing dispatch, transportation, inventory tracking, and delivery coordination. Ensures timely shipment, vendor coordination, documentation, and smooth supply chain operations</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pest control operator</t>
+          <t>German Language Expert (HR Operations)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HERBS VECTOR MANAGMENT SERVICES</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Vee technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bengaluru Urban, Karnataka</t>
+        </is>
+      </c>
       <c r="D54" t="b">
         <v>0</v>
       </c>
@@ -4369,26 +4361,26 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10000.0 - 12000.0</t>
+          <t>400000.0 - 800000.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>10000</v>
+        <v>400000</v>
       </c>
       <c r="M54" t="n">
-        <v>12000</v>
+        <v>800000</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-05-02T19:07:09.301249Z</t>
+          <t>2026-05-16T18:25:08.084884Z</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2885420</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2913805</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4398,28 +4390,32 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>hotel , hospital. college fild work , no target based job, location raipur chhattisgarh .acomodation free</t>
+          <t>Job Title: HR Operations Associates Shift Timings: 1 PM to 11 PM IST.CTC :- As per market&amp;nbsp;Location:- Bengalore Must have skill: Proficient in German Speaking and Writing (B1 / C1+)Good to have skill: HRO Skill Hire to Retire, MS office Shift Timings: 1 PM to 11 PM IST. Should be comfortable wit</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TECHNICIAN</t>
+          <t>Executive - Recruitments</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MAHAKALI TRADERS</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Kapgrow Corporate Advisory Services Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
       <c r="D55" t="b">
         <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4439,26 +4435,26 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>12000.0 - 30000.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="M55" t="n">
-        <v>1500000</v>
+        <v>30000</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-05-01T16:48:09.182415Z</t>
+          <t>2026-05-16T11:37:31.718883Z</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2884256</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2913516</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4468,19 +4464,19 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>TECHNICIAN IN REFIGIRATION AND ABLE TO INSTALL AC AND REFIGIRATORS IN ALL INDIA LEVEL AND COMPLETE WORK OF REFIGIRATION</t>
+          <t>Seeking an Executive - Recruitments to manage end-to-end hiring processes for consultancy clients, ensuring top talent acquisition. Responsibilities include sourcing, screening, scheduling interviews, and coordinating with clients to fulfill recruitment needs efficiently. Requirements: Bachelor’s de</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CARPENTER</t>
+          <t>Sales Administration and Commercial Officer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RS HR</t>
+          <t>Saira People Tech Solutions Private Limited</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -4509,26 +4505,26 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>300000.0 - 800000.0</t>
+          <t>400000.0 - 600000.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="M56" t="n">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-05-01T03:20:30.801545Z</t>
+          <t>2026-05-13T12:11:40.495052Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2884212</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2906366</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4538,32 +4534,28 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>field and warehouse comfortable Carpenter plywood work and wood work pvc work door work everything aembly and repair in furniture product</t>
+          <t>Administrative support for Project Sales Team, Advanced MS Excel, SAP tool, Accounting and Taxation knowledge, Reporting skills, Vendor management, Commercial knowledge. Accurate dealer level sales reports as per requirement. Logistics and operational support to Unit level initiatives.Employee life</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LIC Agent</t>
+          <t>Project Technical Support-III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LIC OF INDIA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>new delhi, DELHI</t>
-        </is>
-      </c>
+          <t>E-SOLUTIONS IT SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="b">
         <v>0</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4581,20 +4573,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1500000</v>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-04-30T20:31:04.037493Z</t>
+          <t>2026-05-13T04:54:40.415881Z</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2884151</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2906121</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4604,32 +4604,28 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Candidate will be selling insurance products Providing after sales services to the customers Market research of the organisation</t>
+          <t>Project entitled-: “Equitable, Quality universal health coverage Implementation research Project for optimizing comprehensive primary health care through Health and Wellness Centres in Primpri Chinchwad Municipal Corporation, Pune district of Maharashtra- EQUIP-HWCs” funded by Indian Council of Medi</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LIC Agent</t>
+          <t>SUPER DISTRIBUTER</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LIC OF INDIA</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>new delhi, DELHI</t>
-        </is>
-      </c>
+          <t>PARTHA SARATHI SERVICES (OPC) PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="b">
         <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4647,20 +4643,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1500000</v>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-04-28T20:31:01.0592Z</t>
+          <t>2026-05-08T10:01:45.831929Z</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2880927</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2897498</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -4670,19 +4674,19 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Candidate will be selling insurance products Providing after sales services to the customers Market research of the organisation</t>
+          <t>Seeking a Super Distributor to drive monthly sales targets by managing and coordinating team efforts across master distributors and distributors. Responsibilities: Achieve monthly sales targets through effective team leadership. Monitor distributor performance and ensure alignment with goals. Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>BANKING JOB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PRERNA CONSULTANCY</t>
+          <t>banking career solution latur,training and placeme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -4711,26 +4715,26 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>25000.0 - 40000.0</t>
+          <t>21000.0 - 25000.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M59" t="n">
         <v>25000</v>
-      </c>
-      <c r="M59" t="n">
-        <v>40000</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-04-23T08:45:18.554261Z</t>
+          <t>2026-05-06T08:30:10.279413Z</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2871625</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2545046</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4740,24 +4744,24 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Seeking a Construction Electrician to install, repair, and maintain electrical systems in construction projects. Full-time role. Responsibilities include wiring, troubleshooting, reading blueprints, and ensuring compliance with safety standards. Requirements: 0-2 years of experience, basic electrica</t>
+          <t>Join this group:- https://chat.whatsapp.com/BlZcHvLh57v0EmygqAT4HF?mode=gi_t 🏦 BANKING CAREER OPPORTUNITY - MAHARASHTRA 🏦 We are hiring for Equitas Small Finance Bank and Kotak Mahindra Bank (NextGen Program). Join one of India's fastest-growing banking sectors! 📅 Online Interview Schedule Process:</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Warehouse Associate</t>
+          <t>Assembly technician</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AASAANJOBS PRIVATE LIMITED</t>
+          <t>Caruna mobility</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abbaiahnahalli b.o, KARNATAKA</t>
+          <t>Ganapathichettikulam, Puducherry</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -4785,26 +4789,26 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15000.0 - 20000.0</t>
+          <t>150000.0 - 240000.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M60" t="n">
-        <v>20000</v>
+        <v>240000</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-04-16T20:30:04.26Z</t>
+          <t>2026-05-05T05:15:17.459479Z</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2861480</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2889551</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -4814,26 +4818,22 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Logistics Executive is responsible for managing dispatch, transportation, inventory tracking, and delivery coordination. Ensures timely shipment, vendor coordination, documentation, and smooth supply chain operations</t>
+          <t>We are looking for assembly specialists, who can also quality check the spare parts coming in from suppliers, for wheelchair fitting. Also automotive wire joining work. Check our products page on website to understand. Technician must also know how to solder. Other skills required include: 1. using</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>insurance policy advisor</t>
+          <t>pest control operator</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>nashik, MAHARASHTRA</t>
-        </is>
-      </c>
+          <t>HERBS VECTOR MANAGMENT SERVICES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="b">
         <v>0</v>
       </c>
@@ -4857,20 +4857,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10000.0 - 12000.0</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M61" t="n">
+        <v>12000</v>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-04-16T20:30:04.915051Z</t>
+          <t>2026-05-02T19:07:09.301249Z</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2861502</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2885420</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4880,19 +4888,19 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>SBI is hiring for Insurance policy advisor across India become certified SBi Insurance advisor and earn good monthly income</t>
+          <t>hotel , hospital. college fild work , no target based job, location raipur chhattisgarh .acomodation free</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Delivery Rider</t>
+          <t>TECHNICIAN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SHREE ENTERPRISE</t>
+          <t>MAHAKALI TRADERS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -4901,7 +4909,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4921,7 +4929,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15000.0 - 25000.0</t>
+          <t>15000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -4930,17 +4938,17 @@
         <v>15000</v>
       </c>
       <c r="M62" t="n">
-        <v>25000</v>
+        <v>1500000</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-04-10T17:22:26.842635Z</t>
+          <t>2026-05-01T16:48:09.182415Z</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2849769</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2884256</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4950,19 +4958,19 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>We are hiring delivery riders for India’s biggest quick commerce company across the country. This is a great opportunity to earn ₹25,000 to ₹40,000 per month. All you need is a bike, the excitement to work hard, and the ambition to become financially independent. Work just 8–9 hours daily, and be pa</t>
+          <t>TECHNICIAN IN REFIGIRATION AND ABLE TO INSTALL AC AND REFIGIRATORS IN ALL INDIA LEVEL AND COMPLETE WORK OF REFIGIRATION</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Life Mitra</t>
+          <t>CARPENTER</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBI LIFE INSURANCE COMPANY LIMITED</t>
+          <t>RS HR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -4971,7 +4979,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4991,26 +4999,26 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>300000.0 - 800000.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>15000</v>
+        <v>300000</v>
       </c>
       <c r="M63" t="n">
-        <v>1500000</v>
+        <v>800000</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-04-09T09:09:11.601871Z</t>
+          <t>2026-05-01T03:20:30.801545Z</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2848567</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2884212</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5020,22 +5028,26 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>A Life Mitra is a commissioned insurance advisor role at SBI Life Insurance that involves identifying customer needs, recommending appropriate insurance products, and building long-term relationships to help clients secure their financial futures. This role offers flexible, full-time or part-time wo</t>
+          <t>field and warehouse comfortable Carpenter plywood work and wood work pvc work door work everything aembly and repair in furniture product</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PWD Deaf</t>
+          <t>LIC Agent</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amazoon.in</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>LIC OF INDIA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>new delhi, DELHI</t>
+        </is>
+      </c>
       <c r="D64" t="b">
         <v>0</v>
       </c>
@@ -5059,28 +5071,20 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>18000.0 - 22000.0</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M64" t="n">
-        <v>22000</v>
-      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-04-08T12:05:09.801657Z</t>
+          <t>2026-04-30T20:31:04.037493Z</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2846129</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2884151</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5090,22 +5094,26 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Amazon PNQ3 – Free Job Opportunity (pwd deaf ) Tomorrow Interview &amp; Sat Joining. 🚹🚺 Male &amp; Female Candidates Welcome 🗓️ Interview Details: ⏰ Time: 08:30 AM 💼 Job Role: * Picking * Packing * Scanning 💰 Salary Structure: * Basic Salary: ₹15,921 * Night Shift Allowance: ₹1,150 * Attendance Bonus: ₹2,80</t>
+          <t>Candidate will be selling insurance products Providing after sales services to the customers Market research of the organisation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Executive Trainee (I&amp;FS and Physics Disciplines)</t>
+          <t>LIC Agent</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nuclear Power Corporation of India Ltd</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>LIC OF INDIA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>new delhi, DELHI</t>
+        </is>
+      </c>
       <c r="D65" t="b">
         <v>0</v>
       </c>
@@ -5129,28 +5137,20 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>76499.0 - 76500.0</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="n">
-        <v>76499</v>
-      </c>
-      <c r="M65" t="n">
-        <v>76500</v>
-      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-04-07T09:37:09.959324Z</t>
+          <t>2026-04-28T20:31:01.0592Z</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2039335</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2880927</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5160,32 +5160,28 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Nuclear Power Corporation of India Limited, A Central Public Sector Enterprise, under Administrative Control of Department of Atomic Energy, Government of India invites online applications for 30 vacancies for the post of Executive Trainee in Industrial &amp; Fire Safety Discipline and Physics Disciplin</t>
+          <t>Candidate will be selling insurance products Providing after sales services to the customers Market research of the organisation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Associates</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SHRIRAM FINANCE LIMITED</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana</t>
-        </is>
-      </c>
+          <t>PRERNA CONSULTANCY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="b">
         <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5205,26 +5201,26 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>25000.0 - 40000.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="M66" t="n">
-        <v>1500000</v>
+        <v>40000</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-03-28T14:50:09.654739Z</t>
+          <t>2026-04-23T08:45:18.554261Z</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2757987</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2871625</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -5234,22 +5230,26 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>We are onboarding Business Associates (Agents) with Shriram Finance Limited. Products to Sell: • Fixed Deposits • Life Insurance • Health Insurance • Vehicle Insurance • Mutual Funds Benefits: • Commission on every policy &amp; investment • No joining fees • No exam • Agent code generated within 1 day •</t>
+          <t>Seeking a Construction Electrician to install, repair, and maintain electrical systems in construction projects. Full-time role. Responsibilities include wiring, troubleshooting, reading blueprints, and ensuring compliance with safety standards. Requirements: 0-2 years of experience, basic electrica</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Home Healthcare</t>
+          <t>Warehouse Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Curagers Healthcare</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>AASAANJOBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>abbaiahnahalli b.o, KARNATAKA</t>
+        </is>
+      </c>
       <c r="D67" t="b">
         <v>0</v>
       </c>
@@ -5275,26 +5275,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20000.0 - 30000.0</t>
+          <t>15000.0 - 20000.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M67" t="n">
         <v>20000</v>
-      </c>
-      <c r="M67" t="n">
-        <v>30000</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-03-24T11:52:01.911168Z</t>
+          <t>2026-04-16T20:30:04.26Z</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2668334</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2861480</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5304,19 +5304,19 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Responsibilities: * Provide patient care with empathy &amp; expertise * Collaborate with healthcare team on treatment plans * Administer medications, monitor vital signs, document findings</t>
+          <t>Logistics Executive is responsible for managing dispatch, transportation, inventory tracking, and delivery coordination. Ensures timely shipment, vendor coordination, documentation, and smooth supply chain operations</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Warehouse associate</t>
+          <t>Life Mitra</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Amazoon.in</t>
+          <t>SBI LIFE INSURANCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>15000.0 - 25000.0</t>
+          <t>15000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -5354,17 +5354,17 @@
         <v>15000</v>
       </c>
       <c r="M68" t="n">
-        <v>25000</v>
+        <v>1500000</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-03-22T02:00:39.688671Z</t>
+          <t>2026-04-09T09:09:11.601871Z</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2656236</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2848567</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Seeking a Warehouse Associate to support daily logistics operations in a fast-paced environment. This is a freelance role. Responsibilities include picking, loading, and assisting with warehouse tasks, ensuring timely and accurate order fulfillment. No prior experience required. Must be physically f</t>
+          <t>A Life Mitra is a commissioned insurance advisor role at SBI Life Insurance that involves identifying customer needs, recommending appropriate insurance products, and building long-term relationships to help clients secure their financial futures. This role offers flexible, full-time or part-time wo</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Warehouse Associate</t>
+          <t>PWD Deaf</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5415,26 +5415,26 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16000.0 - 25000.0</t>
+          <t>18000.0 - 22000.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="M69" t="n">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-03-21T04:48:54.464785Z</t>
+          <t>2026-04-08T12:05:09.801657Z</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2654746</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2846129</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -5444,19 +5444,19 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>* Pick, pack and scan customer orders accurately * Maintain proper inventory and stock records * Use handheld scanners and warehouse systems * Ensure timely dispatch of orders * Follow safety guidelines and company policies * Load and unload goods when required * Maintain cleanliness and organizatio</t>
+          <t>Amazon PNQ3 – Free Job Opportunity (pwd deaf ) Tomorrow Interview &amp; Sat Joining. 🚹🚺 Male &amp; Female Candidates Welcome 🗓️ Interview Details: ⏰ Time: 08:30 AM 💼 Job Role: * Picking * Packing * Scanning 💰 Salary Structure: * Basic Salary: ₹15,921 * Night Shift Allowance: ₹1,150 * Attendance Bonus: ₹2,80</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Packing , Scanning ,Loading , Unloading</t>
+          <t>Executive Trainee (I&amp;FS and Physics Disciplines)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SUNRISING STAFFING SERVICES PRIVATE LIMITED</t>
+          <t>Nuclear Power Corporation of India Ltd</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5485,26 +5485,26 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>12592.0 - 16779.0</t>
+          <t>76499.0 - 76500.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
-        <v>12592</v>
+        <v>76499</v>
       </c>
       <c r="M70" t="n">
-        <v>16779</v>
+        <v>76500</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-03-19T10:18:03.053257Z</t>
+          <t>2026-04-07T09:37:09.959324Z</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2651619</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2039335</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -5514,28 +5514,32 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>*Hiring In Amazon Full Time &amp; Part TIme* ➡️Profile - Picking - Packing , Loading - Unloading *💸Delhi PT Salary - 12592 + PF +ESIC* • Insentives • Attendance Bonus *Part Time 5 Hours Work Rotational Shift* 📍Location :- •Delhi NCR ➡️Required Documents •Aadhar Card •Bank Passbook •Email id •Mobile No •</t>
+          <t>Nuclear Power Corporation of India Limited, A Central Public Sector Enterprise, under Administrative Control of Department of Atomic Energy, Government of India invites online applications for 30 vacancies for the post of Executive Trainee in Industrial &amp; Fire Safety Discipline and Physics Disciplin</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WAREHOUSE ASSOCIATE</t>
+          <t>Business Associates</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INTEXLOGISTICS INDIA PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>SHRIRAM FINANCE LIMITED</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana</t>
+        </is>
+      </c>
       <c r="D71" t="b">
         <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5555,26 +5559,26 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>250000.0 - 275000.0</t>
+          <t>15000.0 - 1500000.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
-        <v>250000</v>
+        <v>15000</v>
       </c>
       <c r="M71" t="n">
-        <v>275000</v>
+        <v>1500000</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-03-18T07:31:17.432238Z</t>
+          <t>2026-03-28T14:50:09.654739Z</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2648789</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2757987</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -5584,26 +5588,22 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Designation Warehouse Associate Role Pick Pack Stow Re-bin Loading/Unloading Job Type Physical: Standing/Walking Job Note: Associates are expected to walk and stand for 9 hrs. Shift Timings Dayshift 8:45am to 6:45pm Night Shift: 6:45pm to 4:45am Note: Two-week day and Two-week Night Working Days 5 d</t>
+          <t>We are onboarding Business Associates (Agents) with Shriram Finance Limited. Products to Sell: • Fixed Deposits • Life Insurance • Health Insurance • Vehicle Insurance • Mutual Funds Benefits: • Commission on every policy &amp; investment • No joining fees • No exam • Agent code generated within 1 day •</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Home Healthcare</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Poonam Ashish Trambadia Conservation Architects</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ahmedabad, Gujarat</t>
-        </is>
-      </c>
+          <t>Curagers Healthcare</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="b">
         <v>0</v>
       </c>
@@ -5629,26 +5629,26 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>20000.0 - 30000.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="M72" t="n">
-        <v>1500000</v>
+        <v>30000</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-03-16T09:26:28.9623Z</t>
+          <t>2026-03-24T11:52:01.911168Z</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>https://betacloud.ncs.gov.in/job-details/2627142</t>
+          <t>https://betacloud.ncs.gov.in/job-details/2668334</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -5658,28 +5658,28 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>This is a full-time role for an Architect/Engineer, based in Ahmedabad with sites across western India. The Architect will be responsible for planning, designing, and overseeing the implementation of architectural projects. Key responsibilities include creating architectural designs, collaborating w</t>
+          <t>Responsibilities: * Provide patient care with empathy &amp; expertise * Collaborate with healthcare team on treatment plans * Administer medications, monitor vital signs, document findings</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Developer Intern</t>
+          <t>Warehouse Associate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SkyTech Digital Labs</t>
+          <t>Amazoon.in</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5699,34 +5699,318 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15000.0 - 1500000.0</t>
+          <t>16000.0 - 25000.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="M73" t="n">
-        <v>1500000</v>
+        <v>25000</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
+          <t>2026-03-21T04:48:54.464785Z</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2654746</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>* Pick, pack and scan customer orders accurately * Maintain proper inventory and stock records * Use handheld scanners and warehouse systems * Ensure timely dispatch of orders * Follow safety guidelines and company policies * Load and unload goods when required * Maintain cleanliness and organizatio</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Packing , Scanning ,Loading , Unloading</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SUNRISING STAFFING SERVICES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>12592.0 - 16779.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>12592</v>
+      </c>
+      <c r="M74" t="n">
+        <v>16779</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-03-19T10:18:03.053257Z</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2651619</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>*Hiring In Amazon Full Time &amp; Part TIme* ➡️Profile - Picking - Packing , Loading - Unloading *💸Delhi PT Salary - 12592 + PF +ESIC* • Insentives • Attendance Bonus *Part Time 5 Hours Work Rotational Shift* 📍Location :- •Delhi NCR ➡️Required Documents •Aadhar Card •Bank Passbook •Email id •Mobile No •</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INTEXLOGISTICS INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>250000.0 - 275000.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M75" t="n">
+        <v>275000</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-03-18T07:31:17.432238Z</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2648789</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Designation Warehouse Associate Role Pick Pack Stow Re-bin Loading/Unloading Job Type Physical: Standing/Walking Job Note: Associates are expected to walk and stand for 9 hrs. Shift Timings Dayshift 8:45am to 6:45pm Night Shift: 6:45pm to 4:45am Note: Two-week day and Two-week Night Working Days 5 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Poonam Ashish Trambadia Conservation Architects</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-03-16T09:26:28.9623Z</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>https://betacloud.ncs.gov.in/job-details/2627142</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>This is a full-time role for an Architect/Engineer, based in Ahmedabad with sites across western India. The Architect will be responsible for planning, designing, and overseeing the implementation of architectural projects. Key responsibilities include creating architectural designs, collaborating w</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SkyTech Digital Labs</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>explicit_pwd</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>custom_api</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>15000.0 - 1500000.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
           <t>2026-03-12T17:39:47.966864Z</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>https://betacloud.ncs.gov.in/job-details/2582059</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>ncs</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>ncs</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>SkyTech Digital Labs is offering a Software Developer Internship for students interested in gaining practical experience in web development and modern technologies. This internship focuses on learning, project-based development, and improving technical skills in a collaborative environment. Location</t>
         </is>
